--- a/public/data/RPA_Project_Tracker_Web_Ready.xlsx
+++ b/public/data/RPA_Project_Tracker_Web_Ready.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KhalidAlharbi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookpro/Desktop/Rac For Project Tracker /Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EE40E6-6516-40E2-8B9D-F73DFDE5D167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992DBAC3-6D0F-0940-A8BD-1A52D3C84363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="4" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="192">
   <si>
     <t>Process / Phase</t>
   </si>
@@ -582,15 +582,56 @@
   </si>
   <si>
     <t>ROI</t>
+  </si>
+  <si>
+    <t>RAC - Ibrahim Al osaimi</t>
+  </si>
+  <si>
+    <t>The access was working for a while, but it has stopped working again.</t>
+  </si>
+  <si>
+    <t>Cyber Security Team</t>
+  </si>
+  <si>
+    <t>Abdulmohsen Abushaiqa</t>
+  </si>
+  <si>
+    <t>ICT</t>
+  </si>
+  <si>
+    <t>Abdulaziz Alodhibi</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>RITM0078287</t>
+  </si>
+  <si>
+    <t>Proven - Mohammed Shalaby</t>
+  </si>
+  <si>
+    <t>Mohammed Shalaby</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Ibrahim Al osaimi</t>
+  </si>
+  <si>
+    <t>Open a Policy Exception ticket, or provide us with the method to access the platform.</t>
+  </si>
+  <si>
+    <t>We cannot complete the setup until access to the platform is granted.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy\ hh:mm"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy\ hh:mm"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -738,16 +779,19 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF17365D"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="19">
@@ -991,7 +1035,7 @@
   <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1002,7 +1046,7 @@
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1020,7 +1064,7 @@
     <xf numFmtId="9" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1029,16 +1073,16 @@
     <xf numFmtId="9" fontId="0" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1047,10 +1091,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="16" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1074,7 +1118,7 @@
     <xf numFmtId="0" fontId="25" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1083,7 +1127,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1104,10 +1148,95 @@
     <xf numFmtId="0" fontId="24" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1195,91 +1324,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1457,7 +1501,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Dashboard"/>
@@ -1715,7 +1758,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O37"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -1727,37 +1770,37 @@
     <col min="14" max="15" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A1" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
+    <row r="2" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
       <c r="N2" s="13" t="s">
         <v>70</v>
       </c>
@@ -1765,22 +1808,22 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A3" s="50" t="str">
+    <row r="3" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A3" s="79" t="str">
         <f ca="1">"Updated: "&amp;TEXT(TODAY(),"dd/mm/yyyy")</f>
-        <v>Updated: 30/07/2026</v>
-      </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
+        <v>Updated: 01/08/2026</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
       <c r="N3" s="13" t="s">
         <v>58</v>
       </c>
@@ -1789,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.65" customHeight="1">
+    <row r="4" spans="1:15" ht="14.75" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1810,27 +1853,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A5" s="51" t="s">
+    <row r="5" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A5" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="64" t="s">
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="71" t="s">
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
       <c r="N5" s="13" t="s">
         <v>11</v>
       </c>
@@ -1839,31 +1882,31 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A6" s="52">
+    <row r="6" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A6" s="81">
         <f>COUNTA('Process Summary'!A4:A33)</f>
         <v>30</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="58">
+      <c r="B6" s="82"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="87">
         <f>AVERAGE('Process Summary'!I4:I33,'Project Tracker'!O2,'Project Tracker'!O7)</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="65">
+        <v>4.8437500000000001E-2</v>
+      </c>
+      <c r="E6" s="88"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="94">
         <f>COUNTIF('Process Summary'!D4:D33,"Completed")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="66"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="72">
+      <c r="H6" s="95"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="101">
         <f ca="1">COUNTIF('Process Summary'!J4:J33,"Red")</f>
         <v>4</v>
       </c>
-      <c r="K6" s="73"/>
-      <c r="L6" s="74"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="103"/>
       <c r="N6" s="13" t="s">
         <v>54</v>
       </c>
@@ -1872,39 +1915,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="74"/>
+    <row r="7" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A7" s="81"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="103"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13"/>
     </row>
-    <row r="8" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A8" s="55"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="77"/>
+    <row r="8" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A8" s="84"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="106"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13"/>
     </row>
-    <row r="9" spans="1:15" ht="14.65" customHeight="1">
+    <row r="9" spans="1:15" ht="14.75" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1920,85 +1963,85 @@
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
     </row>
-    <row r="10" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A10" s="86" t="s">
+    <row r="10" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A10" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="93" t="s">
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="100" t="s">
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="78" t="s">
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="K10" s="78"/>
-      <c r="L10" s="78"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
     </row>
-    <row r="11" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A11" s="87">
+    <row r="11" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A11" s="58">
         <f>COUNTIF('Process Summary'!D4:D33,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="B11" s="88"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="94">
+      <c r="B11" s="59"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="65">
         <f>COUNTIF('Process Summary'!D4:D33,"Not Started")</f>
         <v>30</v>
       </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="101">
+      <c r="E11" s="66"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="72">
         <f>COUNTIF('Process Summary'!D4:D33,"On Hold")</f>
         <v>0</v>
       </c>
-      <c r="H11" s="102"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="79">
+      <c r="H11" s="73"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="50">
         <f ca="1">COUNTIF('Process Summary'!J4:J33,"Amber")</f>
         <v>0</v>
       </c>
-      <c r="K11" s="80"/>
-      <c r="L11" s="81"/>
-    </row>
-    <row r="12" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A12" s="87"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="80"/>
-      <c r="L12" s="81"/>
-    </row>
-    <row r="13" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A13" s="90"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="84"/>
-    </row>
-    <row r="14" spans="1:15" ht="14.65" customHeight="1">
+      <c r="K11" s="51"/>
+      <c r="L11" s="52"/>
+    </row>
+    <row r="12" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A12" s="58"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="52"/>
+    </row>
+    <row r="13" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A13" s="61"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="55"/>
+    </row>
+    <row r="14" spans="1:15" ht="14.75" customHeight="1">
       <c r="A14" s="31"/>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
@@ -2012,7 +2055,7 @@
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
     </row>
-    <row r="15" spans="1:15" ht="14.65" customHeight="1">
+    <row r="15" spans="1:15" ht="14.75" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -2026,25 +2069,25 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="14.65" customHeight="1">
-      <c r="A16" s="85" t="s">
+    <row r="16" spans="1:15" ht="14.75" customHeight="1">
+      <c r="A16" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="85"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="H16" s="85"/>
-      <c r="I16" s="85"/>
-      <c r="J16" s="85"/>
-      <c r="K16" s="85"/>
-      <c r="L16" s="85"/>
-    </row>
-    <row r="17" spans="1:12" ht="14.65" customHeight="1">
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+    </row>
+    <row r="17" spans="1:12" ht="14.75" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>85</v>
       </c>
@@ -2072,7 +2115,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" ht="14.65" customHeight="1">
+    <row r="18" spans="1:12" ht="14.75" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>89</v>
       </c>
@@ -2104,7 +2147,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12" ht="14.65" customHeight="1">
+    <row r="19" spans="1:12" ht="14.75" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>91</v>
       </c>
@@ -2136,7 +2179,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="1:12" ht="14.65" customHeight="1">
+    <row r="20" spans="1:12" ht="14.75" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>93</v>
       </c>
@@ -2168,7 +2211,7 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:12" ht="14.65" customHeight="1">
+    <row r="21" spans="1:12" ht="14.75" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>95</v>
       </c>
@@ -2200,7 +2243,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="14.65" customHeight="1">
+    <row r="22" spans="1:12" ht="14.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>97</v>
       </c>
@@ -2224,7 +2267,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="14.65" customHeight="1">
+    <row r="23" spans="1:12" ht="14.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>98</v>
       </c>
@@ -2248,7 +2291,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" spans="1:12" ht="14.65" customHeight="1">
+    <row r="24" spans="1:12" ht="14.75" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2262,7 +2305,7 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:12" ht="14.65" customHeight="1">
+    <row r="25" spans="1:12" ht="14.75" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2276,25 +2319,25 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="14.65" customHeight="1">
-      <c r="A26" s="85" t="s">
+    <row r="26" spans="1:12" ht="14.75" customHeight="1">
+      <c r="A26" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="85"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="85"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85" t="s">
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-    </row>
-    <row r="27" spans="1:12" ht="14.65" customHeight="1">
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="56"/>
+    </row>
+    <row r="27" spans="1:12" ht="14.75" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>2</v>
       </c>
@@ -2319,7 +2362,7 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
-    <row r="28" spans="1:12" ht="14.65" customHeight="1">
+    <row r="28" spans="1:12" ht="14.75" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>47</v>
       </c>
@@ -2346,7 +2389,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:12" ht="14.65" customHeight="1">
+    <row r="29" spans="1:12" ht="14.75" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>51</v>
       </c>
@@ -2373,7 +2416,7 @@
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="14.65" customHeight="1">
+    <row r="30" spans="1:12" ht="14.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>55</v>
       </c>
@@ -2400,7 +2443,7 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="14.65" customHeight="1">
+    <row r="31" spans="1:12" ht="14.75" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>59</v>
       </c>
@@ -2422,7 +2465,7 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="14.65" customHeight="1">
+    <row r="32" spans="1:12" ht="14.75" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2436,7 +2479,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" spans="1:12" ht="14.65" customHeight="1">
+    <row r="33" spans="1:12" ht="14.75" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2450,7 +2493,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" ht="14.65" customHeight="1">
+    <row r="34" spans="1:12" ht="14.75" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2464,7 +2507,7 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" ht="14.65" customHeight="1">
+    <row r="35" spans="1:12" ht="14.75" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2478,7 +2521,7 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" ht="14.65" customHeight="1">
+    <row r="36" spans="1:12" ht="14.75" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2492,7 +2535,7 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
     </row>
-    <row r="37" spans="1:12" ht="14.65" customHeight="1">
+    <row r="37" spans="1:12" ht="14.75" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2508,6 +2551,16 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C8"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F8"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I8"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J6:L8"/>
     <mergeCell ref="J10:L10"/>
     <mergeCell ref="J11:L13"/>
     <mergeCell ref="A16:F16"/>
@@ -2520,16 +2573,6 @@
     <mergeCell ref="D11:F13"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="G11:I13"/>
-    <mergeCell ref="A1:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C8"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F8"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G6:I8"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J6:L8"/>
   </mergeCells>
   <conditionalFormatting sqref="D18:D23">
     <cfRule type="dataBar" priority="1">
@@ -2576,16 +2619,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.58203125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="50.5" style="16" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.9140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.5" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.1640625" style="16" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.6640625" style="16"/>
@@ -3815,34 +3858,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z222"/>
-  <sheetFormatPr defaultRowHeight="21" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="21" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" style="16" customWidth="1"/>
-    <col min="4" max="4" width="21.4140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.08203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.75" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.08203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.4140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.08203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.25" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.75" style="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" style="16" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.25" style="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.9140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.58203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.08203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.9140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" style="16" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="16" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" style="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="72.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.5" style="16" bestFit="1" customWidth="1"/>
     <col min="27" max="16384" width="8.6640625" style="16"/>
   </cols>
   <sheetData>
@@ -3985,13 +4028,17 @@
       <c r="D3" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="23" t="s">
+        <v>182</v>
+      </c>
       <c r="F3" s="23"/>
       <c r="G3" s="27"/>
       <c r="H3" s="21"/>
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
+      <c r="K3" s="23" t="s">
+        <v>178</v>
+      </c>
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
       <c r="N3" s="27" t="s">
@@ -4032,13 +4079,17 @@
       <c r="D4" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="23" t="s">
+        <v>182</v>
+      </c>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
+      <c r="K4" s="23" t="s">
+        <v>178</v>
+      </c>
       <c r="L4" s="23"/>
       <c r="M4" s="23"/>
       <c r="N4" s="27" t="s">
@@ -4077,16 +4128,28 @@
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
       <c r="D5" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
+        <v>171</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>183</v>
+      </c>
       <c r="G5" s="27"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
+      <c r="H5" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="I5" s="27"/>
+      <c r="J5" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>185</v>
+      </c>
       <c r="M5" s="23"/>
       <c r="N5" s="27" t="s">
         <v>58</v>
@@ -4112,28 +4175,40 @@
         <v>Green</v>
       </c>
       <c r="V5" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="W5" s="23"/>
-      <c r="X5" s="23"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="23"/>
+        <v>188</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="X5" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y5" s="25">
+        <v>46233</v>
+      </c>
+      <c r="Z5" s="23" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="6" spans="1:26" ht="21" customHeight="1">
       <c r="A6" s="23"/>
       <c r="B6" s="23"/>
       <c r="C6" s="23"/>
       <c r="D6" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+        <v>170</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>182</v>
+      </c>
       <c r="G6" s="27"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>186</v>
+      </c>
       <c r="M6" s="23"/>
       <c r="N6" s="27" t="s">
         <v>58</v>
@@ -4184,13 +4259,12 @@
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
-      <c r="N7" s="20" t="str">
-        <f>IF(O3=100%,"Completed",IF(N4="On Hold","On Hold",IF(N5="On Hold","On Hold",IF(N6="On Hold","On Hold",IF(N7="On Hold","On Hold",IF(N8="On Hold","On Hold",IF(N9="On Hold","On Hold",IF(O3&gt;0%,"In Progress","Not Started"))))))))</f>
-        <v>Completed</v>
+      <c r="N7" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="O7" s="18">
-        <f>(O3*3+O4*5+O5+O6*IF(G2="LOW",13,IF(G2="MEDIUM",23,33)))/(9+IF(G2="LOW",13,IF(G2="MEDIUM",23,33)))</f>
-        <v>1</v>
+        <f>AVERAGE(O8:O11)</f>
+        <v>0.55000000000000004</v>
       </c>
       <c r="P7" s="19">
         <f>P8</f>
@@ -4204,11 +4278,11 @@
       <c r="S7" s="19"/>
       <c r="T7" s="48">
         <f ca="1">IF(N7="Cancelled","",IF(S7&lt;&gt;"",S7-Q7,IF(AND(N7&lt;&gt;"Completed",TODAY()&gt;Q7),TODAY()-Q7,0)))</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U7" s="17" t="str">
         <f t="shared" ref="U7:U11" ca="1" si="3">IF(N7="Cancelled","Gray",IF(N7="On Hold","Red",IF(N7="Completed",IF(T7&gt;5,"Red",IF(T7&gt;0,"Amber","Green")),IF(T7&gt;5,"Red",IF(T7&gt;0,"Amber","Green")))))</f>
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="V7" s="35" t="s">
         <v>130</v>
@@ -4225,13 +4299,17 @@
       <c r="D8" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="23" t="s">
+        <v>182</v>
+      </c>
       <c r="F8" s="23"/>
       <c r="G8" s="27"/>
       <c r="H8" s="21"/>
       <c r="I8" s="47"/>
       <c r="J8" s="47"/>
-      <c r="K8" s="23"/>
+      <c r="K8" s="23" t="s">
+        <v>178</v>
+      </c>
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
       <c r="N8" s="27" t="s">
@@ -4272,13 +4350,17 @@
       <c r="D9" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="23" t="s">
+        <v>182</v>
+      </c>
       <c r="F9" s="23"/>
       <c r="G9" s="27"/>
       <c r="H9" s="21"/>
       <c r="I9" s="47"/>
       <c r="J9" s="47"/>
-      <c r="K9" s="23"/>
+      <c r="K9" s="23" t="s">
+        <v>178</v>
+      </c>
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="27" t="s">
@@ -4317,23 +4399,32 @@
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+        <v>171</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>189</v>
+      </c>
       <c r="G10" s="27"/>
-      <c r="H10" s="21"/>
+      <c r="H10" s="21" t="s">
+        <v>184</v>
+      </c>
       <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="23"/>
+      <c r="J10" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>178</v>
+      </c>
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="27" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="O10" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P10" s="47">
         <v>46360</v>
@@ -4345,42 +4436,56 @@
       <c r="S10" s="23"/>
       <c r="T10" s="20">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U10" s="20" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="V10" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
+        <v>188</v>
+      </c>
+      <c r="W10" t="s">
+        <v>190</v>
+      </c>
+      <c r="X10" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y10" s="25">
+        <v>46233</v>
+      </c>
+      <c r="Z10" s="23" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="11" spans="1:26" ht="21" customHeight="1">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="E11" s="23"/>
+        <v>170</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>182</v>
+      </c>
       <c r="F11" s="23"/>
       <c r="G11" s="27"/>
       <c r="H11" s="21"/>
       <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="23"/>
+      <c r="J11" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>186</v>
+      </c>
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="27" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="O11" s="21">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="47">
         <v>46360</v>
@@ -4392,16 +4497,18 @@
       <c r="S11" s="23"/>
       <c r="T11" s="20">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U11" s="20" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="V11" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="W11" s="23"/>
+      <c r="W11" s="23" t="s">
+        <v>191</v>
+      </c>
       <c r="X11" s="23"/>
       <c r="Y11" s="23"/>
       <c r="Z11" s="23"/>
@@ -4540,7 +4647,7 @@
       </c>
       <c r="T13" s="17">
         <f t="shared" ref="T13:T76" ca="1" si="6">IF(N13="Cancelled","",IF(S13&lt;&gt;"",S13-Q13,IF(AND(N13&lt;&gt;"Completed",TODAY()&gt;Q13),TODAY()-Q13,0)))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U13" s="17" t="str">
         <f t="shared" ref="U13:U76" ca="1" si="7">IF(N13="Cancelled","Gray",IF(N13="On Hold","Red",IF(N13="Completed",IF(T13&gt;5,"Red",IF(T13&gt;0,"Amber","Green")),IF(T13&gt;5,"Red",IF(T13&gt;0,"Amber","Green")))))</f>
@@ -4603,7 +4710,7 @@
       <c r="S14" s="28"/>
       <c r="T14" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U14" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4666,7 +4773,7 @@
       <c r="S15" s="28"/>
       <c r="T15" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U15" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4729,7 +4836,7 @@
       <c r="S16" s="28"/>
       <c r="T16" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U16" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4792,7 +4899,7 @@
       <c r="S17" s="28"/>
       <c r="T17" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="U17" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4855,7 +4962,7 @@
       <c r="S18" s="28"/>
       <c r="T18" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U18" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4918,7 +5025,7 @@
       <c r="S19" s="28"/>
       <c r="T19" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U19" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4990,7 +5097,7 @@
       </c>
       <c r="T20" s="17">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U20" s="17" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5053,7 +5160,7 @@
       <c r="S21" s="28"/>
       <c r="T21" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U21" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5116,7 +5223,7 @@
       <c r="S22" s="28"/>
       <c r="T22" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U22" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5179,7 +5286,7 @@
       <c r="S23" s="28"/>
       <c r="T23" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U23" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5242,7 +5349,7 @@
       <c r="S24" s="28"/>
       <c r="T24" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U24" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5305,7 +5412,7 @@
       <c r="S25" s="28"/>
       <c r="T25" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U25" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5368,7 +5475,7 @@
       <c r="S26" s="28"/>
       <c r="T26" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U26" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5440,7 +5547,7 @@
       </c>
       <c r="T27" s="17">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U27" s="17" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5503,7 +5610,7 @@
       <c r="S28" s="28"/>
       <c r="T28" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U28" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5566,7 +5673,7 @@
       <c r="S29" s="28"/>
       <c r="T29" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U29" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5629,7 +5736,7 @@
       <c r="S30" s="28"/>
       <c r="T30" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U30" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5692,7 +5799,7 @@
       <c r="S31" s="28"/>
       <c r="T31" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="U31" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5755,7 +5862,7 @@
       <c r="S32" s="28"/>
       <c r="T32" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U32" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5818,7 +5925,7 @@
       <c r="S33" s="28"/>
       <c r="T33" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U33" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5890,7 +5997,7 @@
       </c>
       <c r="T34" s="17">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U34" s="17" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5953,7 +6060,7 @@
       <c r="S35" s="28"/>
       <c r="T35" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U35" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6016,7 +6123,7 @@
       <c r="S36" s="28"/>
       <c r="T36" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U36" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6079,7 +6186,7 @@
       <c r="S37" s="28"/>
       <c r="T37" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U37" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6142,7 +6249,7 @@
       <c r="S38" s="28"/>
       <c r="T38" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="U38" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6205,7 +6312,7 @@
       <c r="S39" s="28"/>
       <c r="T39" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U39" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6268,7 +6375,7 @@
       <c r="S40" s="28"/>
       <c r="T40" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U40" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6403,7 +6510,7 @@
       <c r="S42" s="28"/>
       <c r="T42" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="U42" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6466,7 +6573,7 @@
       <c r="S43" s="28"/>
       <c r="T43" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U43" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6529,7 +6636,7 @@
       <c r="S44" s="28"/>
       <c r="T44" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U44" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6853,7 +6960,7 @@
       <c r="S49" s="28"/>
       <c r="T49" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U49" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6916,7 +7023,7 @@
       <c r="S50" s="28"/>
       <c r="T50" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U50" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6979,11 +7086,11 @@
       <c r="S51" s="28"/>
       <c r="T51" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U51" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>Green</v>
+        <v>Amber</v>
       </c>
       <c r="V51" s="38" t="s">
         <v>130</v>
@@ -7303,7 +7410,7 @@
       <c r="S56" s="28"/>
       <c r="T56" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U56" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -7366,7 +7473,7 @@
       <c r="S57" s="28"/>
       <c r="T57" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U57" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -7429,11 +7536,11 @@
       <c r="S58" s="28"/>
       <c r="T58" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U58" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>Green</v>
+        <v>Amber</v>
       </c>
       <c r="V58" s="38" t="s">
         <v>130</v>
@@ -7753,7 +7860,7 @@
       <c r="S63" s="28"/>
       <c r="T63" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U63" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -7816,7 +7923,7 @@
       <c r="S64" s="28"/>
       <c r="T64" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U64" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -7879,11 +7986,11 @@
       <c r="S65" s="28"/>
       <c r="T65" s="20">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U65" s="20" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>Green</v>
+        <v>Amber</v>
       </c>
       <c r="V65" s="38" t="s">
         <v>130</v>
@@ -17988,27 +18095,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A12:Z222" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="H5:H6 H3 H8:H11">
-    <cfRule type="dataBar" priority="43">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="44">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EE540B03-4C84-4AD4-A414-502E5F8EF2F5}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="O2:O7">
     <cfRule type="dataBar" priority="21">
       <dataBar>
@@ -18100,8 +18186,29 @@
       <formula>U13="Gray"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H5 H3 H8:H11">
+    <cfRule type="dataBar" priority="45">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="46">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{EE540B03-4C84-4AD4-A414-502E5F8EF2F5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" sqref="N13:N222 G3 G5:G11 N2:N6 N8:N11" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="N13:N222 G3 N8:N11 N2:N6 G5:G11 H6:I6 I5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,On Hold,Completed,Cancelled"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="Z13:Z222" xr:uid="{2D62D783-F530-42BA-B632-A529B3310D65}">
@@ -18121,17 +18228,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EE540B03-4C84-4AD4-A414-502E5F8EF2F5}">
-            <x14:dataBar>
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-              <x14:negativeFillColor auto="1"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>H5:H6 H3 H8:H11</xm:sqref>
-        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{75CBFE49-CFA1-42D4-81EE-DB4D77576ECC}">
             <x14:dataBar>
@@ -18165,6 +18261,17 @@
           </x14:cfRule>
           <xm:sqref>O13:O222</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{EE540B03-4C84-4AD4-A414-502E5F8EF2F5}">
+            <x14:dataBar>
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:negativeFillColor auto="1"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H5 H3 H8:H11</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -18173,7 +18280,7 @@
           <x14:formula1>
             <xm:f>Settings!$D$4:$D$8</xm:f>
           </x14:formula1>
-          <xm:sqref>N14:N19 N217:N222 N210:N215 N203:N208 N196:N201 N189:N194 N182:N187 N175:N180 N168:N173 N161:N166 N154:N159 N147:N152 N140:N145 N133:N138 N126:N131 N119:N124 N112:N117 N105:N110 N98:N103 N91:N96 N84:N89 N77:N82 N70:N75 N63:N68 N56:N61 N49:N54 N42:N47 N35:N40 N28:N33 N21:N26 G3 G5:G11 N3:N6 N8:N11</xm:sqref>
+          <xm:sqref>N14:N19 N217:N222 N210:N215 N203:N208 N196:N201 N189:N194 N182:N187 N175:N180 N168:N173 N161:N166 N154:N159 N147:N152 N140:N145 N133:N138 N126:N131 N119:N124 N112:N117 N105:N110 N98:N103 N91:N96 N84:N89 N77:N82 N70:N75 N63:N68 N56:N61 N49:N54 N42:N47 N35:N40 N28:N33 N21:N26 G3 N8:N11 N3:N6 G5:G11 H6:I6 I5</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -18184,12 +18291,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20">
+    <row r="1" spans="1:8" ht="21">
       <c r="A1" s="108" t="s">
         <v>41</v>
       </c>

--- a/public/data/RPA_Project_Tracker_Web_Ready.xlsx
+++ b/public/data/RPA_Project_Tracker_Web_Ready.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA222"/>
+  <dimension ref="A1:AA221"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="34.83203125" customWidth="1"/>
@@ -1346,105 +1346,105 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Process ID</v>
+        <v>RPA-001</v>
       </c>
       <c r="B12" t="str">
-        <v xml:space="preserve">Process </v>
-      </c>
-      <c r="C12" t="str">
-        <v>ROI</v>
+        <v>Fixed Asset Month end closing</v>
+      </c>
+      <c r="C12">
+        <v>21840</v>
       </c>
       <c r="D12" t="str">
-        <v>Process / Phase</v>
+        <v>Process Summary</v>
       </c>
       <c r="E12" t="str">
-        <v>Department</v>
+        <v>Finance</v>
       </c>
       <c r="F12" t="str">
-        <v>Business Owner</v>
+        <v>Fatimah Alqurashi</v>
       </c>
       <c r="G12" t="str">
-        <v>Complexity</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>Priority</v>
+        <v>Medium</v>
       </c>
       <c r="I12" t="str">
-        <v>Developer</v>
+        <v/>
       </c>
       <c r="J12" t="str">
-        <v>Current Owner</v>
+        <v>Fatimah Alqurashi</v>
       </c>
       <c r="K12" t="str">
-        <v>Responsibility</v>
+        <v>Fatimah Alqurashi</v>
       </c>
       <c r="L12" t="str">
-        <v>Waiting For</v>
+        <v/>
       </c>
       <c r="M12" t="str">
-        <v>Next Action</v>
+        <v/>
       </c>
       <c r="N12" t="str">
-        <v>Status ▼</v>
-      </c>
-      <c r="O12" t="str">
-        <v>Progress</v>
-      </c>
-      <c r="P12" t="str">
-        <v xml:space="preserve">Start </v>
-      </c>
-      <c r="Q12" t="str">
-        <v>Finish</v>
-      </c>
-      <c r="R12" t="str">
-        <v>Days</v>
+        <v>In Progress</v>
+      </c>
+      <c r="O12">
+        <v>0.48235294117647054</v>
+      </c>
+      <c r="P12" s="1" t="d">
+        <v>2026-08-01T23:59:08.000Z</v>
+      </c>
+      <c r="Q12" s="1" t="d">
+        <v>2026-08-26T23:59:08.000Z</v>
+      </c>
+      <c r="R12">
+        <v>17</v>
       </c>
       <c r="S12" t="str">
-        <v>Actual Start▼</v>
+        <v/>
       </c>
       <c r="T12" t="str">
-        <v>Actual Finish▼</v>
-      </c>
-      <c r="U12" t="str">
-        <v>Variance Days</v>
+        <v/>
+      </c>
+      <c r="U12">
+        <v>0</v>
       </c>
       <c r="V12" t="str">
-        <v>Health</v>
+        <v>Green</v>
       </c>
       <c r="W12" t="str">
-        <v>Blocked</v>
+        <v>No</v>
       </c>
       <c r="X12" t="str">
-        <v>Blocker Description</v>
+        <v/>
       </c>
       <c r="Y12" t="str">
-        <v>Delay Reason</v>
+        <v/>
       </c>
       <c r="Z12" t="str">
-        <v>Last Updated</v>
+        <v/>
       </c>
       <c r="AA12" t="str">
-        <v>Updated By</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>RPA-001</v>
+        <v/>
       </c>
       <c r="B13" t="str">
-        <v>Fixed Asset Month end closing</v>
-      </c>
-      <c r="C13">
-        <v>21840</v>
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E13" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>Fatimah Alqurashi</v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1456,10 +1456,10 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>Fatimah Alqurashi</v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="K13" t="str">
-        <v>Fatimah Alqurashi</v>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1468,19 +1468,19 @@
         <v/>
       </c>
       <c r="N13" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O13">
-        <v>0.6333333333333333</v>
+        <v>1</v>
       </c>
       <c r="P13" s="1" t="d">
         <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="Q13" s="1" t="d">
-        <v>2026-08-19T23:59:08.000Z</v>
+        <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="R13">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="S13" t="str">
         <v/>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="D14" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -1563,7 +1563,7 @@
         <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="str">
         <v/>
@@ -1604,13 +1604,13 @@
         <v/>
       </c>
       <c r="D15" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Mohammed Adel</v>
+        <v>Fatimah Alqurashi / Abdulmajeed S. Almutairi</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1622,13 +1622,13 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>Mohammed Adel</v>
+        <v>Fatimah Alqurashi / Abdulmajeed S. Almutairi</v>
       </c>
       <c r="K15" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>The process has been merged, and the required SAP T-Codes have been requested to complete the remaining development.</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1646,7 +1646,7 @@
         <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="R15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="str">
         <v/>
@@ -1687,13 +1687,13 @@
         <v/>
       </c>
       <c r="D16" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Fatimah Alqurashi / Abdulmajeed S. Almutairi</v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1705,31 +1705,31 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>Fatimah Alqurashi / Abdulmajeed S. Almutairi</v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="K16" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L16" t="str">
-        <v>The process has been merged, and the required SAP T-Codes have been requested to complete the remaining development.</v>
+        <v/>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P16" s="1" t="d">
-        <v>2026-08-01T23:59:08.000Z</v>
+        <v>2026-08-02T23:59:08.000Z</v>
       </c>
       <c r="Q16" s="1" t="d">
-        <v>2026-08-01T23:59:08.000Z</v>
+        <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S16" t="str">
         <v/>
@@ -1770,7 +1770,7 @@
         <v/>
       </c>
       <c r="D17" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1788,10 +1788,10 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>Mohammed Shalaby</v>
+        <v>Mohammed Shalaby / Fatimah Alqurashi / Abdulmajeed S. Almutairi</v>
       </c>
       <c r="K17" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1800,19 +1800,19 @@
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O17">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P17" s="1" t="d">
-        <v>2026-08-02T23:59:08.000Z</v>
+        <v>2026-08-16T23:59:08.000Z</v>
       </c>
       <c r="Q17" s="1" t="d">
-        <v>2026-08-12T23:59:08.000Z</v>
+        <v>2026-08-16T23:59:08.000Z</v>
       </c>
       <c r="R17">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S17" t="str">
         <v/>
@@ -1853,7 +1853,7 @@
         <v/>
       </c>
       <c r="D18" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1871,10 +1871,10 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>Mohammed Shalaby / Fatimah Alqurashi / Abdulmajeed S. Almutairi</v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="K18" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1889,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="P18" s="1" t="d">
-        <v>2026-08-16T23:59:08.000Z</v>
+        <v>2026-08-19T23:59:08.000Z</v>
       </c>
       <c r="Q18" s="1" t="d">
-        <v>2026-08-16T23:59:08.000Z</v>
+        <v>2026-08-26T23:59:08.000Z</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S18" t="str">
         <v/>
@@ -1927,25 +1927,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>RPA-002</v>
       </c>
       <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v/>
+        <v>Vendor Payment Status Request</v>
+      </c>
+      <c r="C19">
+        <v>182000</v>
       </c>
       <c r="D19" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>Shared Services</v>
       </c>
       <c r="F19" t="str">
-        <v>Mohammed Shalaby</v>
+        <v>Hani A. Aljihani</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>MEDIUM</v>
       </c>
       <c r="H19" t="str">
         <v>Medium</v>
@@ -1954,10 +1954,10 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>Mohammed Shalaby</v>
+        <v>Hani A. Aljihani</v>
       </c>
       <c r="K19" t="str">
-        <v>Development Team – Proven</v>
+        <v>Hani A. Aljihani</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1966,19 +1966,19 @@
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>0.060000000000000005</v>
       </c>
       <c r="P19" s="1" t="d">
-        <v>2026-08-19T23:59:08.000Z</v>
+        <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="Q19" s="1" t="d">
-        <v>2026-08-19T23:59:08.000Z</v>
+        <v>2026-08-24T23:59:08.000Z</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S19" t="str">
         <v/>
@@ -2010,22 +2010,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>RPA-002</v>
+        <v/>
       </c>
       <c r="B20" t="str">
-        <v>Vendor Payment Status Request</v>
-      </c>
-      <c r="C20">
-        <v>182000</v>
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
       </c>
       <c r="D20" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E20" t="str">
-        <v>Shared Services</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>Hani A. Aljihani</v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="G20" t="str">
         <v>MEDIUM</v>
@@ -2037,10 +2037,10 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Hani A. Aljihani</v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="K20" t="str">
-        <v>Hani A. Aljihani</v>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -2049,19 +2049,19 @@
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O20">
-        <v>0.3228571428571429</v>
+        <v>1</v>
       </c>
       <c r="P20" s="1" t="d">
         <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="Q20" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="R20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S20" t="str">
         <v/>
@@ -2102,7 +2102,7 @@
         <v/>
       </c>
       <c r="D21" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -2185,13 +2185,13 @@
         <v/>
       </c>
       <c r="D22" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Mohammed Adel</v>
+        <v>Hani A. Aljihani</v>
       </c>
       <c r="G22" t="str">
         <v>MEDIUM</v>
@@ -2203,10 +2203,10 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>Mohammed Adel</v>
+        <v>Hani A. Aljihani</v>
       </c>
       <c r="K22" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -2227,7 +2227,7 @@
         <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="R22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="str">
         <v/>
@@ -2257,7 +2257,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" xml:space="preserve">
       <c r="A23" t="str">
         <v/>
       </c>
@@ -2268,13 +2268,13 @@
         <v/>
       </c>
       <c r="D23" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Hani A. Aljihani</v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="G23" t="str">
         <v>MEDIUM</v>
@@ -2286,31 +2286,32 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>Hani A. Aljihani</v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="K23" t="str">
-        <v>Process Owner – RAC</v>
-      </c>
-      <c r="L23" t="str">
-        <v/>
+        <v>Development Team – Proven</v>
+      </c>
+      <c r="L23" t="str" xml:space="preserve">
+        <v xml:space="preserve">SAP Web access, the required SAP T-Codes, and sample vendor emails following the agreed template _x000d_
+(including PO Number, Invoice Number(s), Invoice Amount, and attachment)</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>RAC - Ibrahim Al Osaimi to provide the required system access, SAP T-Codes, and input samples.</v>
       </c>
       <c r="N23" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P23" s="1" t="d">
         <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="Q23" s="1" t="d">
-        <v>2026-08-01T23:59:08.000Z</v>
+        <v>2026-08-11T23:59:08.000Z</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S23" t="str">
         <v/>
@@ -2325,22 +2326,23 @@
         <v>Green</v>
       </c>
       <c r="W23" t="str">
-        <v>No</v>
-      </c>
-      <c r="X23" t="str">
-        <v/>
+        <v>Yes</v>
+      </c>
+      <c r="X23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Development and testing cannot proceed until all required system access, _x000d_
+T-Codes, and input samples are provided.</v>
       </c>
       <c r="Y23" t="str">
         <v/>
       </c>
-      <c r="Z23" t="str">
-        <v/>
+      <c r="Z23" s="1" t="d">
+        <v>2026-07-29T23:59:08.000Z</v>
       </c>
       <c r="AA23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
+        <v>Abdulmohsen Abushaiqa</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="str">
         <v/>
       </c>
@@ -2351,7 +2353,7 @@
         <v/>
       </c>
       <c r="D24" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -2369,32 +2371,31 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>Hussain Khubrany</v>
+        <v>Hussain Khubrany / Hani A. Aljihani</v>
       </c>
       <c r="K24" t="str">
-        <v>Development Team – Proven</v>
-      </c>
-      <c r="L24" t="str" xml:space="preserve">
-        <v xml:space="preserve">SAP Web access, the required SAP T-Codes, and sample vendor emails following the agreed template _x000d_
-(including PO Number, Invoice Number(s), Invoice Amount, and attachment)</v>
+        <v>Proven Development Team / RAC SME</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
       </c>
       <c r="M24" t="str">
-        <v>RAC - Ibrahim Al Osaimi to provide the required system access, SAP T-Codes, and input samples.</v>
+        <v/>
       </c>
       <c r="N24" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O24">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="1" t="d">
-        <v>2026-08-01T23:59:08.000Z</v>
+        <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="Q24" s="1" t="d">
-        <v>2026-08-11T23:59:08.000Z</v>
+        <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="R24">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S24" t="str">
         <v/>
@@ -2409,20 +2410,19 @@
         <v>Green</v>
       </c>
       <c r="W24" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="X24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Development and testing cannot proceed until all required system access, _x000d_
-T-Codes, and input samples are provided.</v>
+        <v>No</v>
+      </c>
+      <c r="X24" t="str">
+        <v/>
       </c>
       <c r="Y24" t="str">
         <v/>
       </c>
-      <c r="Z24" s="1" t="d">
-        <v>2026-07-29T23:59:08.000Z</v>
+      <c r="Z24" t="str">
+        <v/>
       </c>
       <c r="AA24" t="str">
-        <v>Abdulmohsen Abushaiqa</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="D25" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -2454,10 +2454,10 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>Hussain Khubrany / Hani A. Aljihani</v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="K25" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
         <v>0</v>
       </c>
       <c r="P25" s="1" t="d">
-        <v>2026-08-12T23:59:08.000Z</v>
+        <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="Q25" s="1" t="d">
-        <v>2026-08-12T23:59:08.000Z</v>
+        <v>2026-08-24T23:59:08.000Z</v>
       </c>
       <c r="R25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S25" t="str">
         <v/>
@@ -2510,25 +2510,25 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>RPA-003</v>
       </c>
       <c r="B26" t="str">
-        <v/>
-      </c>
-      <c r="C26" t="str">
-        <v/>
+        <v>AP Reports</v>
+      </c>
+      <c r="C26">
+        <v>100800</v>
       </c>
       <c r="D26" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>Finance</v>
       </c>
       <c r="F26" t="str">
-        <v>Hussain Khubrany</v>
+        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
       </c>
       <c r="G26" t="str">
-        <v>MEDIUM</v>
+        <v/>
       </c>
       <c r="H26" t="str">
         <v>Medium</v>
@@ -2537,10 +2537,10 @@
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>Hussain Khubrany</v>
+        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
       </c>
       <c r="K26" t="str">
-        <v>Development Team – Proven</v>
+        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -2549,19 +2549,19 @@
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>0.11764705882352941</v>
       </c>
       <c r="P26" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-08-02T23:59:08.000Z</v>
       </c>
       <c r="Q26" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="R26">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="S26" t="str">
         <v/>
@@ -2593,22 +2593,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>RPA-003</v>
+        <v/>
       </c>
       <c r="B27" t="str">
-        <v>AP Reports</v>
-      </c>
-      <c r="C27">
-        <v>100800</v>
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
       </c>
       <c r="D27" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E27" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F27" t="str">
-        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
+        <v>Eman Saria</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
+        <v>Eman Saria</v>
       </c>
       <c r="K27" t="str">
-        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -2632,19 +2632,19 @@
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O27">
-        <v>0.5166666666666667</v>
+        <v>1</v>
       </c>
       <c r="P27" s="1" t="d">
         <v>2026-08-02T23:59:08.000Z</v>
       </c>
       <c r="Q27" s="1" t="d">
-        <v>2026-08-22T23:59:08.000Z</v>
+        <v>2026-08-02T23:59:08.000Z</v>
       </c>
       <c r="R27">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="S27" t="str">
         <v/>
@@ -2685,7 +2685,7 @@
         <v/>
       </c>
       <c r="D28" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -2727,7 +2727,7 @@
         <v>2026-08-02T23:59:08.000Z</v>
       </c>
       <c r="R28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="str">
         <v/>
@@ -2768,13 +2768,13 @@
         <v/>
       </c>
       <c r="D29" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Eman Saria</v>
+        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2786,10 +2786,10 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>Eman Saria</v>
+        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
       </c>
       <c r="K29" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -2810,7 +2810,7 @@
         <v>2026-08-02T23:59:08.000Z</v>
       </c>
       <c r="R29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="str">
         <v/>
@@ -2851,13 +2851,13 @@
         <v/>
       </c>
       <c r="D30" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2869,31 +2869,31 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="K30" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>SAP GUI access, access to the required SAP T-Code (FBL1N), the AP Vendor Input Report from the SME (Excel attachment), and the vendor mapping file (Vendor ID → Vendor Email) from the</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>RAC – Ibrahim Al Osaimi to provide the required SAP access, T-Code, AP Vendor Input Report, and vendor mapping file.</v>
       </c>
       <c r="N30" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O30">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P30" s="1" t="d">
-        <v>2026-08-02T23:59:08.000Z</v>
+        <v>2026-08-03T23:59:08.000Z</v>
       </c>
       <c r="Q30" s="1" t="d">
-        <v>2026-08-02T23:59:08.000Z</v>
+        <v>2026-08-16T23:59:08.000Z</v>
       </c>
       <c r="R30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S30" t="str">
         <v/>
@@ -2908,19 +2908,19 @@
         <v>Green</v>
       </c>
       <c r="W30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="X30" t="str">
-        <v/>
+        <v>Development and testing cannot proceed until the required system access, T-Code, input report, and vendor mapping file are provided.</v>
       </c>
       <c r="Y30" t="str">
         <v/>
       </c>
-      <c r="Z30" t="str">
-        <v/>
+      <c r="Z30" s="1" t="d">
+        <v>2026-07-29T23:59:08.000Z</v>
       </c>
       <c r="AA30" t="str">
-        <v/>
+        <v>Abdulmohsen Abushaiqa</v>
       </c>
     </row>
     <row r="31">
@@ -2934,7 +2934,7 @@
         <v/>
       </c>
       <c r="D31" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -2952,31 +2952,31 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>Faisal Aljallali</v>
+        <v>Faisal Aljallali / Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
       </c>
       <c r="K31" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L31" t="str">
-        <v>SAP GUI access, access to the required SAP T-Code (FBL1N), the AP Vendor Input Report from the SME (Excel attachment), and the vendor mapping file (Vendor ID → Vendor Email) from the</v>
+        <v/>
       </c>
       <c r="M31" t="str">
-        <v>RAC – Ibrahim Al Osaimi to provide the required SAP access, T-Code, AP Vendor Input Report, and vendor mapping file.</v>
+        <v/>
       </c>
       <c r="N31" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O31">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="1" t="d">
-        <v>2026-08-03T23:59:08.000Z</v>
+        <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="Q31" s="1" t="d">
-        <v>2026-08-16T23:59:08.000Z</v>
+        <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="R31">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S31" t="str">
         <v/>
@@ -2991,19 +2991,19 @@
         <v>Green</v>
       </c>
       <c r="W31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="X31" t="str">
-        <v>Development and testing cannot proceed until the required system access, T-Code, input report, and vendor mapping file are provided.</v>
+        <v/>
       </c>
       <c r="Y31" t="str">
         <v/>
       </c>
-      <c r="Z31" s="1" t="d">
-        <v>2026-07-29T23:59:08.000Z</v>
+      <c r="Z31" t="str">
+        <v/>
       </c>
       <c r="AA31" t="str">
-        <v>Abdulmohsen Abushaiqa</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -3017,7 +3017,7 @@
         <v/>
       </c>
       <c r="D32" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -3035,10 +3035,10 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>Faisal Aljallali / Sarah M. Alshaikh Mubarak / Abdul R. Sattar</v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="K32" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -3053,13 +3053,13 @@
         <v>0</v>
       </c>
       <c r="P32" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-08-22T23:59:08.000Z</v>
       </c>
       <c r="Q32" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="R32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S32" t="str">
         <v/>
@@ -3091,25 +3091,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v>RPA-004</v>
       </c>
       <c r="B33" t="str">
-        <v/>
-      </c>
-      <c r="C33" t="str">
-        <v/>
+        <v>AP Invoice</v>
+      </c>
+      <c r="C33">
+        <v>182000</v>
       </c>
       <c r="D33" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>Finance</v>
       </c>
       <c r="F33" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>High</v>
       </c>
       <c r="H33" t="str">
         <v>Medium</v>
@@ -3118,10 +3118,10 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K33" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -3130,19 +3130,19 @@
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>0.09803921568627451</v>
       </c>
       <c r="P33" s="1" t="d">
-        <v>2026-08-22T23:59:08.000Z</v>
+        <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="Q33" s="1" t="d">
-        <v>2026-08-22T23:59:08.000Z</v>
+        <v>2026-10-13T23:59:08.000Z</v>
       </c>
       <c r="R33">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="S33" t="str">
         <v/>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>RPA-004</v>
+        <v/>
       </c>
       <c r="B34" t="str">
-        <v>AP Invoice</v>
-      </c>
-      <c r="C34">
-        <v>182000</v>
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
       </c>
       <c r="D34" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E34" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F34" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="G34" t="str">
         <v>High</v>
@@ -3201,10 +3201,10 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v/>
       </c>
       <c r="N34" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O34">
-        <v>0.12222222222222222</v>
+        <v>1</v>
       </c>
       <c r="P34" s="1" t="d">
         <v>2026-08-01T23:59:08.000Z</v>
       </c>
       <c r="Q34" s="1" t="d">
-        <v>2026-10-06T23:59:08.000Z</v>
+        <v>2026-08-05T23:59:08.000Z</v>
       </c>
       <c r="R34">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="S34" t="str">
         <v/>
@@ -3266,7 +3266,7 @@
         <v/>
       </c>
       <c r="D35" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -3296,10 +3296,10 @@
         <v/>
       </c>
       <c r="N35" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P35" s="1" t="d">
         <v>2026-08-01T23:59:08.000Z</v>
@@ -3308,7 +3308,7 @@
         <v>2026-08-05T23:59:08.000Z</v>
       </c>
       <c r="R35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S35" t="str">
         <v/>
@@ -3349,13 +3349,13 @@
         <v/>
       </c>
       <c r="D36" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Waleed Hamza</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G36" t="str">
         <v>High</v>
@@ -3367,10 +3367,10 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>Waleed Hamza</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K36" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -3379,19 +3379,19 @@
         <v/>
       </c>
       <c r="N36" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O36">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P36" s="1" t="d">
-        <v>2026-08-01T23:59:08.000Z</v>
+        <v>2026-08-05T23:59:08.000Z</v>
       </c>
       <c r="Q36" s="1" t="d">
         <v>2026-08-05T23:59:08.000Z</v>
       </c>
       <c r="R36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S36" t="str">
         <v/>
@@ -3432,13 +3432,13 @@
         <v/>
       </c>
       <c r="D37" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Ayman</v>
       </c>
       <c r="G37" t="str">
         <v>High</v>
@@ -3450,10 +3450,10 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Ayman</v>
       </c>
       <c r="K37" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -3468,13 +3468,13 @@
         <v>0</v>
       </c>
       <c r="P37" s="1" t="d">
-        <v>2026-08-05T23:59:08.000Z</v>
+        <v>2026-08-08T23:59:08.000Z</v>
       </c>
       <c r="Q37" s="1" t="d">
-        <v>2026-08-05T23:59:08.000Z</v>
+        <v>2026-09-30T23:59:08.000Z</v>
       </c>
       <c r="R37">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="S37" t="str">
         <v/>
@@ -3515,7 +3515,7 @@
         <v/>
       </c>
       <c r="D38" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -3533,10 +3533,10 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Ayman / Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K38" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -3551,13 +3551,13 @@
         <v>0</v>
       </c>
       <c r="P38" s="1" t="d">
-        <v>2026-08-08T23:59:08.000Z</v>
+        <v>2026-10-03T23:59:08.000Z</v>
       </c>
       <c r="Q38" s="1" t="d">
-        <v>2026-09-30T23:59:08.000Z</v>
+        <v>2026-10-03T23:59:08.000Z</v>
       </c>
       <c r="R38">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="S38" t="str">
         <v/>
@@ -3598,7 +3598,7 @@
         <v/>
       </c>
       <c r="D39" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -3616,10 +3616,10 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v xml:space="preserve">Ayman / Sarah M. Alshaikh Mubarak </v>
+        <v>Ayman</v>
       </c>
       <c r="K39" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -3634,13 +3634,13 @@
         <v>0</v>
       </c>
       <c r="P39" s="1" t="d">
-        <v>2026-10-03T23:59:08.000Z</v>
+        <v>2026-10-06T23:59:08.000Z</v>
       </c>
       <c r="Q39" s="1" t="d">
-        <v>2026-10-03T23:59:08.000Z</v>
+        <v>2026-10-13T23:59:08.000Z</v>
       </c>
       <c r="R39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S39" t="str">
         <v/>
@@ -3672,25 +3672,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>RPA-005</v>
       </c>
       <c r="B40" t="str">
-        <v/>
-      </c>
-      <c r="C40" t="str">
-        <v/>
+        <v>Invoice Verifications and Processing</v>
+      </c>
+      <c r="C40">
+        <v>100100</v>
       </c>
       <c r="D40" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>Shared Services</v>
       </c>
       <c r="F40" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="G40" t="str">
-        <v>High</v>
+        <v/>
       </c>
       <c r="H40" t="str">
         <v>Medium</v>
@@ -3699,10 +3699,10 @@
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="K40" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -3711,19 +3711,19 @@
         <v/>
       </c>
       <c r="N40" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>0.11363636363636363</v>
       </c>
       <c r="P40" s="1" t="d">
-        <v>2026-10-06T23:59:08.000Z</v>
+        <v>2026-08-03T23:59:08.000Z</v>
       </c>
       <c r="Q40" s="1" t="d">
         <v>2026-10-06T23:59:08.000Z</v>
       </c>
       <c r="R40">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="S40" t="str">
         <v/>
@@ -3755,22 +3755,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>RPA-005</v>
+        <v/>
       </c>
       <c r="B41" t="str">
-        <v>Invoice Verifications and Processing</v>
-      </c>
-      <c r="C41">
-        <v>100100</v>
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
       </c>
       <c r="D41" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E41" t="str">
-        <v>Shared Services</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Eman Saria</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -3782,10 +3782,10 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Eman Saria</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -3794,19 +3794,19 @@
         <v/>
       </c>
       <c r="N41" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O41">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="P41" s="1" t="d">
         <v>2026-08-03T23:59:08.000Z</v>
       </c>
       <c r="Q41" s="1" t="d">
-        <v>2026-09-29T23:59:08.000Z</v>
+        <v>2026-08-09T23:59:08.000Z</v>
       </c>
       <c r="R41">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="S41" t="str">
         <v/>
@@ -3847,7 +3847,7 @@
         <v/>
       </c>
       <c r="D42" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -3877,19 +3877,19 @@
         <v/>
       </c>
       <c r="N42" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O42">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P42" s="1" t="d">
-        <v>2026-08-03T23:59:08.000Z</v>
+        <v>2026-08-09T23:59:08.000Z</v>
       </c>
       <c r="Q42" s="1" t="d">
         <v>2026-08-09T23:59:08.000Z</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S42" t="str">
         <v/>
@@ -3930,13 +3930,13 @@
         <v/>
       </c>
       <c r="D43" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Eman Saria</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -3948,10 +3948,10 @@
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>Eman Saria</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="K43" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -3960,19 +3960,19 @@
         <v/>
       </c>
       <c r="N43" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O43">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P43" s="1" t="d">
-        <v>2026-08-09T23:59:08.000Z</v>
+        <v>2026-08-10T23:59:08.000Z</v>
       </c>
       <c r="Q43" s="1" t="d">
-        <v>2026-08-09T23:59:08.000Z</v>
+        <v>2026-08-10T23:59:08.000Z</v>
       </c>
       <c r="R43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="str">
         <v/>
@@ -4013,13 +4013,13 @@
         <v/>
       </c>
       <c r="D44" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -4031,10 +4031,10 @@
         <v/>
       </c>
       <c r="J44" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="K44" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -4052,10 +4052,10 @@
         <v>2026-08-10T23:59:08.000Z</v>
       </c>
       <c r="Q44" s="1" t="d">
-        <v>2026-08-10T23:59:08.000Z</v>
+        <v>2026-09-23T23:59:08.000Z</v>
       </c>
       <c r="R44">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="S44" t="str">
         <v/>
@@ -4096,7 +4096,7 @@
         <v/>
       </c>
       <c r="D45" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -4114,10 +4114,10 @@
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>Mohammed Shalaby</v>
+        <v xml:space="preserve">Mohammed Shalaby / Bshaier </v>
       </c>
       <c r="K45" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -4132,13 +4132,13 @@
         <v>0</v>
       </c>
       <c r="P45" s="1" t="d">
-        <v>2026-08-10T23:59:08.000Z</v>
+        <v>2026-09-26T23:59:08.000Z</v>
       </c>
       <c r="Q45" s="1" t="d">
-        <v>2026-09-23T23:59:08.000Z</v>
+        <v>2026-09-26T23:59:08.000Z</v>
       </c>
       <c r="R45">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="S45" t="str">
         <v/>
@@ -4179,7 +4179,7 @@
         <v/>
       </c>
       <c r="D46" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -4197,10 +4197,10 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v xml:space="preserve">Mohammed Shalaby / Bshaier </v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="K46" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -4215,13 +4215,13 @@
         <v>0</v>
       </c>
       <c r="P46" s="1" t="d">
-        <v>2026-09-26T23:59:08.000Z</v>
+        <v>2026-09-29T23:59:08.000Z</v>
       </c>
       <c r="Q46" s="1" t="d">
-        <v>2026-09-26T23:59:08.000Z</v>
+        <v>2026-10-06T23:59:08.000Z</v>
       </c>
       <c r="R46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S46" t="str">
         <v/>
@@ -4253,25 +4253,25 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v/>
+        <v>RPA-006</v>
       </c>
       <c r="B47" t="str">
-        <v/>
-      </c>
-      <c r="C47" t="str">
-        <v/>
+        <v>Sick Leave Requests</v>
+      </c>
+      <c r="C47">
+        <v>75833</v>
       </c>
       <c r="D47" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>HR</v>
       </c>
       <c r="F47" t="str">
-        <v>Mohammed Shalaby</v>
+        <v xml:space="preserve">Sultan N.Almunaykhir </v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>Low</v>
       </c>
       <c r="H47" t="str">
         <v>Medium</v>
@@ -4280,10 +4280,10 @@
         <v/>
       </c>
       <c r="J47" t="str">
-        <v>Mohammed Shalaby</v>
+        <v xml:space="preserve">Sultan N.Almunaykhir </v>
       </c>
       <c r="K47" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -4292,19 +4292,19 @@
         <v/>
       </c>
       <c r="N47" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47" s="1" t="d">
-        <v>2026-09-29T23:59:08.000Z</v>
+        <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="Q47" s="1" t="d">
-        <v>2026-09-29T23:59:08.000Z</v>
+        <v>2026-09-05T23:59:08.000Z</v>
       </c>
       <c r="R47">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="S47" t="str">
         <v/>
@@ -4336,22 +4336,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>RPA-006</v>
+        <v/>
       </c>
       <c r="B48" t="str">
-        <v>Sick Leave Requests</v>
-      </c>
-      <c r="C48">
-        <v>75833</v>
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
       </c>
       <c r="D48" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E48" t="str">
-        <v>HR</v>
+        <v/>
       </c>
       <c r="F48" t="str">
-        <v xml:space="preserve">Sultan N.Almunaykhir </v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="G48" t="str">
         <v>Low</v>
@@ -4363,10 +4363,10 @@
         <v/>
       </c>
       <c r="J48" t="str">
-        <v xml:space="preserve">Sultan N.Almunaykhir </v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -4375,19 +4375,19 @@
         <v/>
       </c>
       <c r="N48" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O48">
-        <v>0.34</v>
+        <v>1</v>
       </c>
       <c r="P48" s="1" t="d">
         <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="Q48" s="1" t="d">
-        <v>2026-08-29T23:59:08.000Z</v>
+        <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="R48">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S48" t="str">
         <v/>
@@ -4428,7 +4428,7 @@
         <v/>
       </c>
       <c r="D49" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -4511,13 +4511,13 @@
         <v/>
       </c>
       <c r="D50" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Waleed Hamza</v>
+        <v xml:space="preserve">Sultan N.Almunaykhir </v>
       </c>
       <c r="G50" t="str">
         <v>Low</v>
@@ -4529,22 +4529,22 @@
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>Waleed Hamza</v>
+        <v xml:space="preserve">Sultan N.Almunaykhir </v>
       </c>
       <c r="K50" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L50" t="str">
-        <v/>
+        <v>Business approval of the PDD</v>
       </c>
       <c r="M50" t="str">
         <v/>
       </c>
       <c r="N50" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O50">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P50" s="1" t="d">
         <v>2026-08-12T23:59:08.000Z</v>
@@ -4553,7 +4553,7 @@
         <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="R50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="str">
         <v/>
@@ -4576,11 +4576,11 @@
       <c r="Y50" t="str">
         <v/>
       </c>
-      <c r="Z50" t="str">
-        <v/>
+      <c r="Z50" s="1" t="d">
+        <v>2026-07-29T23:59:08.000Z</v>
       </c>
       <c r="AA50" t="str">
-        <v/>
+        <v>Mohammed Adel</v>
       </c>
     </row>
     <row r="51">
@@ -4594,13 +4594,13 @@
         <v/>
       </c>
       <c r="D51" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v xml:space="preserve">Sultan N.Almunaykhir </v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="G51" t="str">
         <v>Low</v>
@@ -4612,31 +4612,31 @@
         <v/>
       </c>
       <c r="J51" t="str">
-        <v xml:space="preserve">Sultan N.Almunaykhir </v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="K51" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L51" t="str">
-        <v>Business approval of the PDD</v>
+        <v/>
       </c>
       <c r="M51" t="str">
         <v/>
       </c>
       <c r="N51" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O51">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P51" s="1" t="d">
         <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="Q51" s="1" t="d">
-        <v>2026-08-12T23:59:08.000Z</v>
+        <v>2026-08-23T23:59:08.000Z</v>
       </c>
       <c r="R51">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S51" t="str">
         <v/>
@@ -4659,11 +4659,11 @@
       <c r="Y51" t="str">
         <v/>
       </c>
-      <c r="Z51" s="1" t="d">
-        <v>2026-07-29T23:59:08.000Z</v>
+      <c r="Z51" t="str">
+        <v/>
       </c>
       <c r="AA51" t="str">
-        <v>Mohammed Adel</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -4677,7 +4677,7 @@
         <v/>
       </c>
       <c r="D52" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -4695,10 +4695,10 @@
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>Hussain Khubrany</v>
+        <v xml:space="preserve">Hussain Khubrany / Sultan N.Almunaykhir </v>
       </c>
       <c r="K52" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -4713,13 +4713,13 @@
         <v>0</v>
       </c>
       <c r="P52" s="1" t="d">
-        <v>2026-08-12T23:59:08.000Z</v>
+        <v>2026-08-24T23:59:08.000Z</v>
       </c>
       <c r="Q52" s="1" t="d">
-        <v>2026-08-23T23:59:08.000Z</v>
+        <v>2026-08-24T23:59:08.000Z</v>
       </c>
       <c r="R52">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S52" t="str">
         <v/>
@@ -4760,7 +4760,7 @@
         <v/>
       </c>
       <c r="D53" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -4778,10 +4778,10 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v xml:space="preserve">Hussain Khubrany / Sultan N.Almunaykhir </v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="K53" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -4796,13 +4796,13 @@
         <v>0</v>
       </c>
       <c r="P53" s="1" t="d">
-        <v>2026-08-24T23:59:08.000Z</v>
+        <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="Q53" s="1" t="d">
-        <v>2026-08-24T23:59:08.000Z</v>
+        <v>2026-09-05T23:59:08.000Z</v>
       </c>
       <c r="R53">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S53" t="str">
         <v/>
@@ -4834,25 +4834,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
+        <v>RPA-007</v>
       </c>
       <c r="B54" t="str">
-        <v/>
-      </c>
-      <c r="C54" t="str">
-        <v/>
+        <v>Non-Aero Invoicing Commercial Posting</v>
+      </c>
+      <c r="C54">
+        <v>72800</v>
       </c>
       <c r="D54" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>Finance</v>
       </c>
       <c r="F54" t="str">
-        <v>Hussain Khubrany</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G54" t="str">
-        <v>Low</v>
+        <v/>
       </c>
       <c r="H54" t="str">
         <v>Medium</v>
@@ -4861,10 +4861,10 @@
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>Hussain Khubrany</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K54" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -4876,16 +4876,16 @@
         <v>Not Started</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="P54" s="1" t="d">
-        <v>2026-08-29T23:59:08.000Z</v>
+        <v>2026-08-08T23:59:08.000Z</v>
       </c>
       <c r="Q54" s="1" t="d">
-        <v>2026-08-29T23:59:08.000Z</v>
+        <v>2026-09-16T23:59:08.000Z</v>
       </c>
       <c r="R54">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="S54" t="str">
         <v/>
@@ -4917,22 +4917,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>RPA-007</v>
+        <v/>
       </c>
       <c r="B55" t="str">
-        <v>Non-Aero Invoicing Commercial Posting</v>
-      </c>
-      <c r="C55">
-        <v>72800</v>
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
       </c>
       <c r="D55" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E55" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F55" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -4944,10 +4944,10 @@
         <v/>
       </c>
       <c r="J55" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -4956,19 +4956,19 @@
         <v/>
       </c>
       <c r="N55" t="str">
-        <v>Not Started</v>
+        <v>Completed</v>
       </c>
       <c r="O55">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P55" s="1" t="d">
         <v>2026-08-08T23:59:08.000Z</v>
       </c>
       <c r="Q55" s="1" t="d">
-        <v>2026-09-09T23:59:08.000Z</v>
+        <v>2026-08-09T23:59:08.000Z</v>
       </c>
       <c r="R55">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="S55" t="str">
         <v/>
@@ -5009,7 +5009,7 @@
         <v/>
       </c>
       <c r="D56" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -5039,10 +5039,10 @@
         <v/>
       </c>
       <c r="N56" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P56" s="1" t="d">
         <v>2026-08-08T23:59:08.000Z</v>
@@ -5051,7 +5051,7 @@
         <v>2026-08-09T23:59:08.000Z</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S56" t="str">
         <v/>
@@ -5092,13 +5092,13 @@
         <v/>
       </c>
       <c r="D57" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Mohammed Adel</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -5110,10 +5110,10 @@
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>Mohammed Adel</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K57" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -5122,19 +5122,19 @@
         <v/>
       </c>
       <c r="N57" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O57">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P57" s="1" t="d">
-        <v>2026-08-08T23:59:08.000Z</v>
+        <v>2026-08-09T23:59:08.000Z</v>
       </c>
       <c r="Q57" s="1" t="d">
         <v>2026-08-09T23:59:08.000Z</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S57" t="str">
         <v/>
@@ -5175,13 +5175,13 @@
         <v/>
       </c>
       <c r="D58" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Ayman</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -5193,10 +5193,10 @@
         <v/>
       </c>
       <c r="J58" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Ayman</v>
       </c>
       <c r="K58" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -5211,13 +5211,13 @@
         <v>0</v>
       </c>
       <c r="P58" s="1" t="d">
-        <v>2026-08-09T23:59:08.000Z</v>
+        <v>2026-08-15T23:59:08.000Z</v>
       </c>
       <c r="Q58" s="1" t="d">
-        <v>2026-08-09T23:59:08.000Z</v>
+        <v>2026-09-05T23:59:08.000Z</v>
       </c>
       <c r="R58">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="S58" t="str">
         <v/>
@@ -5258,7 +5258,7 @@
         <v/>
       </c>
       <c r="D59" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -5276,10 +5276,10 @@
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Ayman / Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K59" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -5294,13 +5294,13 @@
         <v>0</v>
       </c>
       <c r="P59" s="1" t="d">
-        <v>2026-08-15T23:59:08.000Z</v>
+        <v>2026-09-06T23:59:08.000Z</v>
       </c>
       <c r="Q59" s="1" t="d">
-        <v>2026-09-05T23:59:08.000Z</v>
+        <v>2026-09-06T23:59:08.000Z</v>
       </c>
       <c r="R59">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="S59" t="str">
         <v/>
@@ -5341,7 +5341,7 @@
         <v/>
       </c>
       <c r="D60" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -5359,10 +5359,10 @@
         <v/>
       </c>
       <c r="J60" t="str">
-        <v xml:space="preserve">Ayman / Sarah M. Alshaikh Mubarak </v>
+        <v>Ayman</v>
       </c>
       <c r="K60" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -5377,13 +5377,13 @@
         <v>0</v>
       </c>
       <c r="P60" s="1" t="d">
-        <v>2026-09-06T23:59:08.000Z</v>
+        <v>2026-09-09T23:59:08.000Z</v>
       </c>
       <c r="Q60" s="1" t="d">
-        <v>2026-09-06T23:59:08.000Z</v>
+        <v>2026-09-16T23:59:08.000Z</v>
       </c>
       <c r="R60">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S60" t="str">
         <v/>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>RPA-008</v>
       </c>
       <c r="B61" t="str">
-        <v/>
-      </c>
-      <c r="C61" t="str">
-        <v/>
+        <v>Capitalize Assets on SAP</v>
+      </c>
+      <c r="C61">
+        <v>72800</v>
       </c>
       <c r="D61" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>Finance</v>
       </c>
       <c r="F61" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -5442,10 +5442,10 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K61" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -5454,19 +5454,19 @@
         <v/>
       </c>
       <c r="N61" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P61" s="1" t="d">
-        <v>2026-09-09T23:59:08.000Z</v>
+        <v>2026-08-10T23:59:08.000Z</v>
       </c>
       <c r="Q61" s="1" t="d">
-        <v>2026-09-09T23:59:08.000Z</v>
+        <v>2026-09-13T23:59:08.000Z</v>
       </c>
       <c r="R61">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="S61" t="str">
         <v/>
@@ -5498,22 +5498,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>RPA-008</v>
+        <v/>
       </c>
       <c r="B62" t="str">
-        <v>Capitalize Assets on SAP</v>
-      </c>
-      <c r="C62">
-        <v>72800</v>
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v/>
       </c>
       <c r="D62" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E62" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F62" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Eman Saria</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -5525,10 +5525,10 @@
         <v/>
       </c>
       <c r="J62" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Eman Saria</v>
       </c>
       <c r="K62" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -5537,19 +5537,19 @@
         <v/>
       </c>
       <c r="N62" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O62">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="P62" s="1" t="d">
         <v>2026-08-10T23:59:08.000Z</v>
       </c>
       <c r="Q62" s="1" t="d">
-        <v>2026-09-06T23:59:08.000Z</v>
+        <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="R62">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="S62" t="str">
         <v/>
@@ -5590,7 +5590,7 @@
         <v/>
       </c>
       <c r="D63" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -5620,10 +5620,10 @@
         <v/>
       </c>
       <c r="N63" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O63">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P63" s="1" t="d">
         <v>2026-08-10T23:59:08.000Z</v>
@@ -5632,7 +5632,7 @@
         <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S63" t="str">
         <v/>
@@ -5673,13 +5673,13 @@
         <v/>
       </c>
       <c r="D64" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Eman Saria</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -5691,10 +5691,10 @@
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>Eman Saria</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K64" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -5703,19 +5703,19 @@
         <v/>
       </c>
       <c r="N64" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O64">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P64" s="1" t="d">
-        <v>2026-08-10T23:59:08.000Z</v>
+        <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="Q64" s="1" t="d">
         <v>2026-08-12T23:59:08.000Z</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S64" t="str">
         <v/>
@@ -5756,13 +5756,13 @@
         <v/>
       </c>
       <c r="D65" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -5774,10 +5774,10 @@
         <v/>
       </c>
       <c r="J65" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="K65" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -5792,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="P65" s="1" t="d">
-        <v>2026-08-12T23:59:08.000Z</v>
+        <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="Q65" s="1" t="d">
-        <v>2026-08-12T23:59:08.000Z</v>
+        <v>2026-08-31T23:59:08.000Z</v>
       </c>
       <c r="R65">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="S65" t="str">
         <v/>
@@ -5839,7 +5839,7 @@
         <v/>
       </c>
       <c r="D66" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -5857,10 +5857,10 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Faisal Aljallali / Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K66" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -5875,13 +5875,13 @@
         <v>0</v>
       </c>
       <c r="P66" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-09-01T23:59:08.000Z</v>
       </c>
       <c r="Q66" s="1" t="d">
-        <v>2026-08-31T23:59:08.000Z</v>
+        <v>2026-09-01T23:59:08.000Z</v>
       </c>
       <c r="R66">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="S66" t="str">
         <v/>
@@ -5922,7 +5922,7 @@
         <v/>
       </c>
       <c r="D67" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -5940,10 +5940,10 @@
         <v/>
       </c>
       <c r="J67" t="str">
-        <v xml:space="preserve">Faisal Aljallali / Sarah M. Alshaikh Mubarak </v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="K67" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="P67" s="1" t="d">
-        <v>2026-09-01T23:59:08.000Z</v>
+        <v>2026-09-06T23:59:08.000Z</v>
       </c>
       <c r="Q67" s="1" t="d">
-        <v>2026-09-01T23:59:08.000Z</v>
+        <v>2026-09-13T23:59:08.000Z</v>
       </c>
       <c r="R67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S67" t="str">
         <v/>
@@ -5996,22 +5996,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v/>
+        <v>RPA-009</v>
       </c>
       <c r="B68" t="str">
-        <v/>
-      </c>
-      <c r="C68" t="str">
-        <v/>
+        <v>Utilities and Facilities Invoicing</v>
+      </c>
+      <c r="C68">
+        <v>67200</v>
       </c>
       <c r="D68" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>Finance</v>
       </c>
       <c r="F68" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -6023,10 +6023,10 @@
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K68" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -6035,19 +6035,19 @@
         <v/>
       </c>
       <c r="N68" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="P68" s="1" t="d">
-        <v>2026-09-06T23:59:08.000Z</v>
+        <v>2026-08-10T23:59:08.000Z</v>
       </c>
       <c r="Q68" s="1" t="d">
-        <v>2026-09-06T23:59:08.000Z</v>
+        <v>2026-10-07T23:59:08.000Z</v>
       </c>
       <c r="R68">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="S68" t="str">
         <v/>
@@ -6079,22 +6079,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>RPA-009</v>
+        <v/>
       </c>
       <c r="B69" t="str">
-        <v>Utilities and Facilities Invoicing</v>
-      </c>
-      <c r="C69">
-        <v>67200</v>
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v/>
       </c>
       <c r="D69" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E69" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F69" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -6106,10 +6106,10 @@
         <v/>
       </c>
       <c r="J69" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="K69" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -6118,19 +6118,19 @@
         <v/>
       </c>
       <c r="N69" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O69">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="P69" s="1" t="d">
         <v>2026-08-10T23:59:08.000Z</v>
       </c>
       <c r="Q69" s="1" t="d">
-        <v>2026-09-30T23:59:08.000Z</v>
+        <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="R69">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="S69" t="str">
         <v/>
@@ -6171,7 +6171,7 @@
         <v/>
       </c>
       <c r="D70" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -6201,10 +6201,10 @@
         <v/>
       </c>
       <c r="N70" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O70">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P70" s="1" t="d">
         <v>2026-08-10T23:59:08.000Z</v>
@@ -6213,7 +6213,7 @@
         <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="R70">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S70" t="str">
         <v/>
@@ -6254,13 +6254,13 @@
         <v/>
       </c>
       <c r="D71" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Mohammed Adel</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -6272,10 +6272,10 @@
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>Mohammed Adel</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K71" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -6284,19 +6284,19 @@
         <v/>
       </c>
       <c r="N71" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O71">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P71" s="1" t="d">
-        <v>2026-08-10T23:59:08.000Z</v>
+        <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="Q71" s="1" t="d">
         <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="R71">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S71" t="str">
         <v/>
@@ -6337,13 +6337,13 @@
         <v/>
       </c>
       <c r="D72" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -6355,10 +6355,10 @@
         <v/>
       </c>
       <c r="J72" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="K72" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -6373,13 +6373,13 @@
         <v>0</v>
       </c>
       <c r="P72" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-08-24T23:59:08.000Z</v>
       </c>
       <c r="Q72" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-09-26T23:59:08.000Z</v>
       </c>
       <c r="R72">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="S72" t="str">
         <v/>
@@ -6420,7 +6420,7 @@
         <v/>
       </c>
       <c r="D73" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -6438,10 +6438,10 @@
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>Mohammed Shalaby</v>
+        <v xml:space="preserve">Mohammed Shalaby / Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K73" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -6456,13 +6456,13 @@
         <v>0</v>
       </c>
       <c r="P73" s="1" t="d">
-        <v>2026-08-24T23:59:08.000Z</v>
+        <v>2026-09-27T23:59:08.000Z</v>
       </c>
       <c r="Q73" s="1" t="d">
-        <v>2026-09-26T23:59:08.000Z</v>
+        <v>2026-09-27T23:59:08.000Z</v>
       </c>
       <c r="R73">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="S73" t="str">
         <v/>
@@ -6503,7 +6503,7 @@
         <v/>
       </c>
       <c r="D74" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -6521,10 +6521,10 @@
         <v/>
       </c>
       <c r="J74" t="str">
-        <v xml:space="preserve">Mohammed Shalaby / Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="K74" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L74" t="str">
         <v/>
@@ -6539,13 +6539,13 @@
         <v>0</v>
       </c>
       <c r="P74" s="1" t="d">
-        <v>2026-09-27T23:59:08.000Z</v>
+        <v>2026-09-30T23:59:08.000Z</v>
       </c>
       <c r="Q74" s="1" t="d">
-        <v>2026-09-27T23:59:08.000Z</v>
+        <v>2026-10-07T23:59:08.000Z</v>
       </c>
       <c r="R74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S74" t="str">
         <v/>
@@ -6577,22 +6577,22 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v/>
+        <v>RPA-010</v>
       </c>
       <c r="B75" t="str">
-        <v/>
-      </c>
-      <c r="C75" t="str">
-        <v/>
+        <v>Shared Services KPI Reporting</v>
+      </c>
+      <c r="C75">
+        <v>66360</v>
       </c>
       <c r="D75" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E75" t="str">
-        <v/>
+        <v>Shared Services</v>
       </c>
       <c r="F75" t="str">
-        <v>Mohammed Shalaby</v>
+        <v>Sarah M. Alsharif</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -6604,10 +6604,10 @@
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>Mohammed Shalaby</v>
+        <v>Sarah M. Alsharif</v>
       </c>
       <c r="K75" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L75" t="str">
         <v/>
@@ -6616,19 +6616,19 @@
         <v/>
       </c>
       <c r="N75" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="P75" s="1" t="d">
-        <v>2026-09-30T23:59:08.000Z</v>
+        <v>2026-08-15T23:59:08.000Z</v>
       </c>
       <c r="Q75" s="1" t="d">
-        <v>2026-09-30T23:59:08.000Z</v>
+        <v>2026-10-05T23:59:08.000Z</v>
       </c>
       <c r="R75">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="S75" t="str">
         <v/>
@@ -6660,22 +6660,22 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>RPA-010</v>
+        <v/>
       </c>
       <c r="B76" t="str">
-        <v>Shared Services KPI Reporting</v>
-      </c>
-      <c r="C76">
-        <v>66360</v>
+        <v/>
+      </c>
+      <c r="C76" t="str">
+        <v/>
       </c>
       <c r="D76" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E76" t="str">
-        <v>Shared Services</v>
+        <v/>
       </c>
       <c r="F76" t="str">
-        <v>Sarah M. Alsharif</v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -6687,10 +6687,10 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>Sarah M. Alsharif</v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="K76" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -6699,19 +6699,19 @@
         <v/>
       </c>
       <c r="N76" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O76">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="P76" s="1" t="d">
         <v>2026-08-15T23:59:08.000Z</v>
       </c>
       <c r="Q76" s="1" t="d">
-        <v>2026-09-28T23:59:08.000Z</v>
+        <v>2026-08-16T23:59:08.000Z</v>
       </c>
       <c r="R76">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="S76" t="str">
         <v/>
@@ -6752,7 +6752,7 @@
         <v/>
       </c>
       <c r="D77" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -6782,10 +6782,10 @@
         <v/>
       </c>
       <c r="N77" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O77">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P77" s="1" t="d">
         <v>2026-08-15T23:59:08.000Z</v>
@@ -6794,7 +6794,7 @@
         <v>2026-08-16T23:59:08.000Z</v>
       </c>
       <c r="R77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S77" t="str">
         <v/>
@@ -6835,13 +6835,13 @@
         <v/>
       </c>
       <c r="D78" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Waleed Hamza</v>
+        <v>Sarah M. Alsharif</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -6853,10 +6853,10 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>Waleed Hamza</v>
+        <v>Sarah M. Alsharif</v>
       </c>
       <c r="K78" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L78" t="str">
         <v/>
@@ -6865,19 +6865,19 @@
         <v/>
       </c>
       <c r="N78" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O78">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P78" s="1" t="d">
-        <v>2026-08-15T23:59:08.000Z</v>
+        <v>2026-08-16T23:59:08.000Z</v>
       </c>
       <c r="Q78" s="1" t="d">
         <v>2026-08-16T23:59:08.000Z</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S78" t="str">
         <v/>
@@ -6918,13 +6918,13 @@
         <v/>
       </c>
       <c r="D79" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Sarah M. Alsharif</v>
+        <v>Ayman</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -6936,10 +6936,10 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>Sarah M. Alsharif</v>
+        <v>Ayman</v>
       </c>
       <c r="K79" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L79" t="str">
         <v/>
@@ -6954,13 +6954,13 @@
         <v>0</v>
       </c>
       <c r="P79" s="1" t="d">
-        <v>2026-08-16T23:59:08.000Z</v>
+        <v>2026-09-01T23:59:08.000Z</v>
       </c>
       <c r="Q79" s="1" t="d">
-        <v>2026-08-16T23:59:08.000Z</v>
+        <v>2026-09-21T23:59:08.000Z</v>
       </c>
       <c r="R79">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S79" t="str">
         <v/>
@@ -7001,7 +7001,7 @@
         <v/>
       </c>
       <c r="D80" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -7019,10 +7019,10 @@
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>Ayman</v>
+        <v>Ayman / Sarah M. Alsharif</v>
       </c>
       <c r="K80" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L80" t="str">
         <v/>
@@ -7037,13 +7037,13 @@
         <v>0</v>
       </c>
       <c r="P80" s="1" t="d">
-        <v>2026-09-01T23:59:08.000Z</v>
+        <v>2026-09-23T23:59:08.000Z</v>
       </c>
       <c r="Q80" s="1" t="d">
-        <v>2026-09-21T23:59:08.000Z</v>
+        <v>2026-09-23T23:59:08.000Z</v>
       </c>
       <c r="R80">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S80" t="str">
         <v/>
@@ -7084,7 +7084,7 @@
         <v/>
       </c>
       <c r="D81" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -7102,10 +7102,10 @@
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>Ayman / Sarah M. Alsharif</v>
+        <v>Ayman</v>
       </c>
       <c r="K81" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L81" t="str">
         <v/>
@@ -7120,13 +7120,13 @@
         <v>0</v>
       </c>
       <c r="P81" s="1" t="d">
-        <v>2026-09-23T23:59:08.000Z</v>
+        <v>2026-09-28T23:59:08.000Z</v>
       </c>
       <c r="Q81" s="1" t="d">
-        <v>2026-09-23T23:59:08.000Z</v>
+        <v>2026-10-05T23:59:08.000Z</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S81" t="str">
         <v/>
@@ -7138,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="V81" t="str">
-        <v>Green</v>
+        <v/>
       </c>
       <c r="W81" t="str">
         <v>No</v>
@@ -7158,22 +7158,22 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v/>
+        <v>RPA-011</v>
       </c>
       <c r="B82" t="str">
-        <v/>
-      </c>
-      <c r="C82" t="str">
-        <v/>
+        <v>Revenue Recognition &amp; Contract Monitoring</v>
+      </c>
+      <c r="C82">
+        <v>63280</v>
       </c>
       <c r="D82" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E82" t="str">
-        <v/>
+        <v>Finance</v>
       </c>
       <c r="F82" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -7185,10 +7185,10 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K82" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L82" t="str">
         <v/>
@@ -7197,19 +7197,19 @@
         <v/>
       </c>
       <c r="N82" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="P82" s="1" t="d">
-        <v>2026-09-28T23:59:08.000Z</v>
+        <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="Q82" s="1" t="d">
-        <v>2026-09-28T23:59:08.000Z</v>
+        <v>2026-10-19T23:59:08.000Z</v>
       </c>
       <c r="R82">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="S82" t="str">
         <v/>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="V82" t="str">
-        <v/>
+        <v>Green</v>
       </c>
       <c r="W82" t="str">
         <v>No</v>
@@ -7241,22 +7241,22 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>RPA-011</v>
+        <v/>
       </c>
       <c r="B83" t="str">
-        <v>Revenue Recognition &amp; Contract Monitoring</v>
-      </c>
-      <c r="C83">
-        <v>63280</v>
+        <v/>
+      </c>
+      <c r="C83" t="str">
+        <v/>
       </c>
       <c r="D83" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E83" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F83" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Eman Saria</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -7268,10 +7268,10 @@
         <v/>
       </c>
       <c r="J83" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Eman Saria</v>
       </c>
       <c r="K83" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L83" t="str">
         <v/>
@@ -7280,19 +7280,19 @@
         <v/>
       </c>
       <c r="N83" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O83">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="P83" s="1" t="d">
         <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="Q83" s="1" t="d">
-        <v>2026-10-12T23:59:08.000Z</v>
+        <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="R83">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="S83" t="str">
         <v/>
@@ -7333,7 +7333,7 @@
         <v/>
       </c>
       <c r="D84" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -7363,10 +7363,10 @@
         <v/>
       </c>
       <c r="N84" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O84">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P84" s="1" t="d">
         <v>2026-08-17T23:59:08.000Z</v>
@@ -7375,7 +7375,7 @@
         <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="R84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="str">
         <v/>
@@ -7416,13 +7416,13 @@
         <v/>
       </c>
       <c r="D85" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Eman Saria</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -7434,10 +7434,10 @@
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>Eman Saria</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K85" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L85" t="str">
         <v/>
@@ -7446,10 +7446,10 @@
         <v/>
       </c>
       <c r="N85" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O85">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P85" s="1" t="d">
         <v>2026-08-17T23:59:08.000Z</v>
@@ -7458,7 +7458,7 @@
         <v>2026-08-17T23:59:08.000Z</v>
       </c>
       <c r="R85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="str">
         <v/>
@@ -7499,13 +7499,13 @@
         <v/>
       </c>
       <c r="D86" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -7517,10 +7517,10 @@
         <v/>
       </c>
       <c r="J86" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="K86" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L86" t="str">
         <v/>
@@ -7535,13 +7535,13 @@
         <v>0</v>
       </c>
       <c r="P86" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-09-06T23:59:08.000Z</v>
       </c>
       <c r="Q86" s="1" t="d">
-        <v>2026-08-17T23:59:08.000Z</v>
+        <v>2026-10-05T23:59:08.000Z</v>
       </c>
       <c r="R86">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="S86" t="str">
         <v/>
@@ -7582,7 +7582,7 @@
         <v/>
       </c>
       <c r="D87" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -7600,10 +7600,10 @@
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Faisal Aljallali / Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K87" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L87" t="str">
         <v/>
@@ -7618,13 +7618,13 @@
         <v>0</v>
       </c>
       <c r="P87" s="1" t="d">
-        <v>2026-09-06T23:59:08.000Z</v>
+        <v>2026-10-07T23:59:08.000Z</v>
       </c>
       <c r="Q87" s="1" t="d">
-        <v>2026-10-05T23:59:08.000Z</v>
+        <v>2026-10-07T23:59:08.000Z</v>
       </c>
       <c r="R87">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="S87" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v/>
       </c>
       <c r="D88" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -7683,10 +7683,10 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v xml:space="preserve">Faisal Aljallali / Sarah M. Alshaikh Mubarak </v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="K88" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L88" t="str">
         <v/>
@@ -7701,13 +7701,13 @@
         <v>0</v>
       </c>
       <c r="P88" s="1" t="d">
-        <v>2026-10-07T23:59:08.000Z</v>
+        <v>2026-10-12T23:59:08.000Z</v>
       </c>
       <c r="Q88" s="1" t="d">
-        <v>2026-10-07T23:59:08.000Z</v>
+        <v>2026-10-19T23:59:08.000Z</v>
       </c>
       <c r="R88">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S88" t="str">
         <v/>
@@ -7739,22 +7739,22 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v/>
+        <v>RPA-012</v>
       </c>
       <c r="B89" t="str">
-        <v/>
-      </c>
-      <c r="C89" t="str">
-        <v/>
+        <v>Banking Reconciliation</v>
+      </c>
+      <c r="C89">
+        <v>49000</v>
       </c>
       <c r="D89" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>Finance</v>
       </c>
       <c r="F89" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -7766,10 +7766,10 @@
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K89" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L89" t="str">
         <v/>
@@ -7778,19 +7778,19 @@
         <v/>
       </c>
       <c r="N89" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="P89" s="1" t="d">
-        <v>2026-10-12T23:59:08.000Z</v>
+        <v>2026-08-18T23:59:08.000Z</v>
       </c>
       <c r="Q89" s="1" t="d">
-        <v>2026-10-12T23:59:08.000Z</v>
+        <v>2026-10-25T23:59:08.000Z</v>
       </c>
       <c r="R89">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="S89" t="str">
         <v/>
@@ -7822,22 +7822,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>RPA-012</v>
+        <v/>
       </c>
       <c r="B90" t="str">
-        <v>Banking Reconciliation</v>
-      </c>
-      <c r="C90">
-        <v>49000</v>
+        <v/>
+      </c>
+      <c r="C90" t="str">
+        <v/>
       </c>
       <c r="D90" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E90" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F90" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -7849,10 +7849,10 @@
         <v/>
       </c>
       <c r="J90" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="K90" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L90" t="str">
         <v/>
@@ -7861,19 +7861,19 @@
         <v/>
       </c>
       <c r="N90" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O90">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="P90" s="1" t="d">
         <v>2026-08-18T23:59:08.000Z</v>
       </c>
       <c r="Q90" s="1" t="d">
-        <v>2026-10-18T23:59:08.000Z</v>
+        <v>2026-08-19T23:59:08.000Z</v>
       </c>
       <c r="R90">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="S90" t="str">
         <v/>
@@ -7914,7 +7914,7 @@
         <v/>
       </c>
       <c r="D91" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -7944,19 +7944,19 @@
         <v/>
       </c>
       <c r="N91" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O91">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P91" s="1" t="d">
-        <v>2026-08-18T23:59:08.000Z</v>
+        <v>2026-08-19T23:59:08.000Z</v>
       </c>
       <c r="Q91" s="1" t="d">
         <v>2026-08-19T23:59:08.000Z</v>
       </c>
       <c r="R91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S91" t="str">
         <v/>
@@ -7997,13 +7997,13 @@
         <v/>
       </c>
       <c r="D92" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Mohammed Adel</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -8015,10 +8015,10 @@
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>Mohammed Adel</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K92" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L92" t="str">
         <v/>
@@ -8027,10 +8027,10 @@
         <v/>
       </c>
       <c r="N92" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O92">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P92" s="1" t="d">
         <v>2026-08-19T23:59:08.000Z</v>
@@ -8039,7 +8039,7 @@
         <v>2026-08-19T23:59:08.000Z</v>
       </c>
       <c r="R92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="str">
         <v/>
@@ -8080,13 +8080,13 @@
         <v/>
       </c>
       <c r="D93" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -8098,10 +8098,10 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="K93" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L93" t="str">
         <v/>
@@ -8116,13 +8116,13 @@
         <v>0</v>
       </c>
       <c r="P93" s="1" t="d">
-        <v>2026-08-19T23:59:08.000Z</v>
+        <v>2026-09-22T23:59:08.000Z</v>
       </c>
       <c r="Q93" s="1" t="d">
-        <v>2026-08-19T23:59:08.000Z</v>
+        <v>2026-10-12T23:59:08.000Z</v>
       </c>
       <c r="R93">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S93" t="str">
         <v/>
@@ -8163,7 +8163,7 @@
         <v/>
       </c>
       <c r="D94" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -8181,10 +8181,10 @@
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>Hussain Khubrany</v>
+        <v xml:space="preserve">Hussain Khubrany / Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K94" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L94" t="str">
         <v/>
@@ -8199,13 +8199,13 @@
         <v>0</v>
       </c>
       <c r="P94" s="1" t="d">
-        <v>2026-09-22T23:59:08.000Z</v>
+        <v>2026-10-13T23:59:08.000Z</v>
       </c>
       <c r="Q94" s="1" t="d">
-        <v>2026-10-12T23:59:08.000Z</v>
+        <v>2026-10-13T23:59:08.000Z</v>
       </c>
       <c r="R94">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="S94" t="str">
         <v/>
@@ -8246,7 +8246,7 @@
         <v/>
       </c>
       <c r="D95" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -8264,10 +8264,10 @@
         <v/>
       </c>
       <c r="J95" t="str">
-        <v xml:space="preserve">Hussain Khubrany / Sarah M. Alshaikh Mubarak </v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="K95" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L95" t="str">
         <v/>
@@ -8282,13 +8282,13 @@
         <v>0</v>
       </c>
       <c r="P95" s="1" t="d">
-        <v>2026-10-13T23:59:08.000Z</v>
+        <v>2026-10-18T23:59:08.000Z</v>
       </c>
       <c r="Q95" s="1" t="d">
-        <v>2026-10-13T23:59:08.000Z</v>
+        <v>2026-10-25T23:59:08.000Z</v>
       </c>
       <c r="R95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S95" t="str">
         <v/>
@@ -8320,22 +8320,22 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v/>
+        <v>RPA-013</v>
       </c>
       <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
-        <v/>
+        <v>Monthly and Annual WHT</v>
+      </c>
+      <c r="C96">
+        <v>48720</v>
       </c>
       <c r="D96" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E96" t="str">
-        <v/>
+        <v>Finance</v>
       </c>
       <c r="F96" t="str">
-        <v>Hussain Khubrany</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -8347,10 +8347,10 @@
         <v/>
       </c>
       <c r="J96" t="str">
-        <v>Hussain Khubrany</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K96" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L96" t="str">
         <v/>
@@ -8359,19 +8359,19 @@
         <v/>
       </c>
       <c r="N96" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>0.27586206896551724</v>
       </c>
       <c r="P96" s="1" t="d">
-        <v>2026-10-18T23:59:08.000Z</v>
+        <v>2026-08-18T23:59:08.000Z</v>
       </c>
       <c r="Q96" s="1" t="d">
-        <v>2026-10-18T23:59:08.000Z</v>
+        <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="R96">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="S96" t="str">
         <v/>
@@ -8403,22 +8403,22 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>RPA-013</v>
+        <v/>
       </c>
       <c r="B97" t="str">
-        <v>Monthly and Annual WHT</v>
-      </c>
-      <c r="C97">
-        <v>48720</v>
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v/>
       </c>
       <c r="D97" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E97" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F97" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -8430,10 +8430,10 @@
         <v/>
       </c>
       <c r="J97" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="K97" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L97" t="str">
         <v/>
@@ -8442,19 +8442,19 @@
         <v/>
       </c>
       <c r="N97" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O97">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="P97" s="1" t="d">
         <v>2026-08-18T23:59:08.000Z</v>
       </c>
       <c r="Q97" s="1" t="d">
-        <v>2026-10-20T23:59:08.000Z</v>
+        <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="R97">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="S97" t="str">
         <v/>
@@ -8495,7 +8495,7 @@
         <v/>
       </c>
       <c r="D98" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -8525,10 +8525,10 @@
         <v/>
       </c>
       <c r="N98" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O98">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P98" s="1" t="d">
         <v>2026-08-18T23:59:08.000Z</v>
@@ -8537,7 +8537,7 @@
         <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="R98">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S98" t="str">
         <v/>
@@ -8578,13 +8578,13 @@
         <v/>
       </c>
       <c r="D99" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Waleed Hamza</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -8596,10 +8596,10 @@
         <v/>
       </c>
       <c r="J99" t="str">
-        <v>Waleed Hamza</v>
+        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K99" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L99" t="str">
         <v/>
@@ -8608,19 +8608,19 @@
         <v/>
       </c>
       <c r="N99" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O99">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P99" s="1" t="d">
-        <v>2026-08-18T23:59:08.000Z</v>
+        <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="Q99" s="1" t="d">
         <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="R99">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S99" t="str">
         <v/>
@@ -8661,13 +8661,13 @@
         <v/>
       </c>
       <c r="D100" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -8679,10 +8679,10 @@
         <v/>
       </c>
       <c r="J100" t="str">
-        <v xml:space="preserve">Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="K100" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L100" t="str">
         <v/>
@@ -8697,13 +8697,13 @@
         <v>0</v>
       </c>
       <c r="P100" s="1" t="d">
-        <v>2026-08-29T23:59:08.000Z</v>
+        <v>2026-09-26T23:59:08.000Z</v>
       </c>
       <c r="Q100" s="1" t="d">
-        <v>2026-08-29T23:59:08.000Z</v>
+        <v>2026-10-13T23:59:08.000Z</v>
       </c>
       <c r="R100">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="S100" t="str">
         <v/>
@@ -8744,7 +8744,7 @@
         <v/>
       </c>
       <c r="D101" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -8762,10 +8762,10 @@
         <v/>
       </c>
       <c r="J101" t="str">
-        <v>Mohammed Shalaby</v>
+        <v xml:space="preserve">Mohammed Shalaby / Sarah M. Alshaikh Mubarak </v>
       </c>
       <c r="K101" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L101" t="str">
         <v/>
@@ -8780,13 +8780,13 @@
         <v>0</v>
       </c>
       <c r="P101" s="1" t="d">
-        <v>2026-09-26T23:59:08.000Z</v>
+        <v>2026-10-17T23:59:08.000Z</v>
       </c>
       <c r="Q101" s="1" t="d">
-        <v>2026-10-13T23:59:08.000Z</v>
+        <v>2026-10-17T23:59:08.000Z</v>
       </c>
       <c r="R101">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="S101" t="str">
         <v/>
@@ -8827,7 +8827,7 @@
         <v/>
       </c>
       <c r="D102" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -8845,10 +8845,10 @@
         <v/>
       </c>
       <c r="J102" t="str">
-        <v xml:space="preserve">Mohammed Shalaby / Sarah M. Alshaikh Mubarak </v>
+        <v>Mohammed Shalaby</v>
       </c>
       <c r="K102" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L102" t="str">
         <v/>
@@ -8863,13 +8863,13 @@
         <v>0</v>
       </c>
       <c r="P102" s="1" t="d">
-        <v>2026-10-17T23:59:08.000Z</v>
+        <v>2026-10-20T23:59:08.000Z</v>
       </c>
       <c r="Q102" s="1" t="d">
-        <v>2026-10-17T23:59:08.000Z</v>
+        <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S102" t="str">
         <v/>
@@ -8901,22 +8901,22 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v/>
+        <v>RPA-014</v>
       </c>
       <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
-        <v/>
+        <v>Create Contract through SAP</v>
+      </c>
+      <c r="C103">
+        <v>36400</v>
       </c>
       <c r="D103" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E103" t="str">
-        <v/>
+        <v>Shared Services</v>
       </c>
       <c r="F103" t="str">
-        <v>Mohammed Shalaby</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -8928,10 +8928,10 @@
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>Mohammed Shalaby</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="K103" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L103" t="str">
         <v/>
@@ -8946,13 +8946,13 @@
         <v>0</v>
       </c>
       <c r="P103" s="1" t="d">
-        <v>2026-10-20T23:59:08.000Z</v>
+        <v>2026-08-22T23:59:08.000Z</v>
       </c>
       <c r="Q103" s="1" t="d">
-        <v>2026-10-20T23:59:08.000Z</v>
+        <v>2026-10-18T23:59:08.000Z</v>
       </c>
       <c r="R103">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S103" t="str">
         <v/>
@@ -8984,22 +8984,22 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>RPA-014</v>
+        <v/>
       </c>
       <c r="B104" t="str">
-        <v>Create Contract through SAP</v>
-      </c>
-      <c r="C104">
-        <v>36400</v>
+        <v/>
+      </c>
+      <c r="C104" t="str">
+        <v/>
       </c>
       <c r="D104" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E104" t="str">
-        <v>Shared Services</v>
+        <v/>
       </c>
       <c r="F104" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Eman Saria</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -9011,10 +9011,10 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Eman Saria</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L104" t="str">
         <v/>
@@ -9032,10 +9032,10 @@
         <v>2026-08-22T23:59:08.000Z</v>
       </c>
       <c r="Q104" s="1" t="d">
-        <v>2026-10-11T23:59:08.000Z</v>
+        <v>2026-08-23T23:59:08.000Z</v>
       </c>
       <c r="R104">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S104" t="str">
         <v/>
@@ -9076,7 +9076,7 @@
         <v/>
       </c>
       <c r="D105" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -9112,13 +9112,13 @@
         <v>0</v>
       </c>
       <c r="P105" s="1" t="d">
-        <v>2026-08-22T23:59:08.000Z</v>
+        <v>2026-08-23T23:59:08.000Z</v>
       </c>
       <c r="Q105" s="1" t="d">
         <v>2026-08-23T23:59:08.000Z</v>
       </c>
       <c r="R105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S105" t="str">
         <v/>
@@ -9159,13 +9159,13 @@
         <v/>
       </c>
       <c r="D106" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Eman Saria</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -9177,10 +9177,10 @@
         <v/>
       </c>
       <c r="J106" t="str">
-        <v>Eman Saria</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="K106" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L106" t="str">
         <v/>
@@ -9201,7 +9201,7 @@
         <v>2026-08-23T23:59:08.000Z</v>
       </c>
       <c r="R106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S106" t="str">
         <v/>
@@ -9242,13 +9242,13 @@
         <v/>
       </c>
       <c r="D107" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Ayman</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -9260,10 +9260,10 @@
         <v/>
       </c>
       <c r="J107" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Ayman</v>
       </c>
       <c r="K107" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L107" t="str">
         <v/>
@@ -9278,13 +9278,13 @@
         <v>0</v>
       </c>
       <c r="P107" s="1" t="d">
-        <v>2026-08-23T23:59:08.000Z</v>
+        <v>2026-09-27T23:59:08.000Z</v>
       </c>
       <c r="Q107" s="1" t="d">
-        <v>2026-08-23T23:59:08.000Z</v>
+        <v>2026-10-05T23:59:08.000Z</v>
       </c>
       <c r="R107">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S107" t="str">
         <v/>
@@ -9325,7 +9325,7 @@
         <v/>
       </c>
       <c r="D108" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -9343,10 +9343,10 @@
         <v/>
       </c>
       <c r="J108" t="str">
-        <v>Ayman</v>
+        <v>Ayman / bshaier</v>
       </c>
       <c r="K108" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L108" t="str">
         <v/>
@@ -9361,13 +9361,13 @@
         <v>0</v>
       </c>
       <c r="P108" s="1" t="d">
-        <v>2026-09-27T23:59:08.000Z</v>
+        <v>2026-10-06T23:59:08.000Z</v>
       </c>
       <c r="Q108" s="1" t="d">
-        <v>2026-10-05T23:59:08.000Z</v>
+        <v>2026-10-06T23:59:08.000Z</v>
       </c>
       <c r="R108">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S108" t="str">
         <v/>
@@ -9408,7 +9408,7 @@
         <v/>
       </c>
       <c r="D109" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -9426,10 +9426,10 @@
         <v/>
       </c>
       <c r="J109" t="str">
-        <v>Ayman / bshaier</v>
+        <v>Ayman</v>
       </c>
       <c r="K109" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L109" t="str">
         <v/>
@@ -9444,13 +9444,13 @@
         <v>0</v>
       </c>
       <c r="P109" s="1" t="d">
-        <v>2026-10-06T23:59:08.000Z</v>
+        <v>2026-10-11T23:59:08.000Z</v>
       </c>
       <c r="Q109" s="1" t="d">
-        <v>2026-10-06T23:59:08.000Z</v>
+        <v>2026-10-18T23:59:08.000Z</v>
       </c>
       <c r="R109">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S109" t="str">
         <v/>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v/>
+        <v>RPA-015</v>
       </c>
       <c r="B110" t="str">
-        <v/>
-      </c>
-      <c r="C110" t="str">
-        <v/>
+        <v>Aero Invoicing Posting</v>
+      </c>
+      <c r="C110">
+        <v>13440</v>
       </c>
       <c r="D110" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E110" t="str">
-        <v/>
+        <v>Finance</v>
       </c>
       <c r="F110" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -9509,10 +9509,10 @@
         <v/>
       </c>
       <c r="J110" t="str">
-        <v>Ayman</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="K110" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L110" t="str">
         <v/>
@@ -9521,19 +9521,19 @@
         <v/>
       </c>
       <c r="N110" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="P110" s="1" t="d">
-        <v>2026-10-11T23:59:08.000Z</v>
+        <v>2026-08-24T23:59:08.000Z</v>
       </c>
       <c r="Q110" s="1" t="d">
-        <v>2026-10-11T23:59:08.000Z</v>
+        <v>2026-11-10T23:59:08.000Z</v>
       </c>
       <c r="R110">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="S110" t="str">
         <v/>
@@ -9565,22 +9565,22 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>RPA-015</v>
+        <v/>
       </c>
       <c r="B111" t="str">
-        <v>Aero Invoicing Posting</v>
-      </c>
-      <c r="C111">
-        <v>13440</v>
+        <v/>
+      </c>
+      <c r="C111" t="str">
+        <v/>
       </c>
       <c r="D111" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E111" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="F111" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -9592,10 +9592,10 @@
         <v/>
       </c>
       <c r="J111" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Mohammed Adel</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L111" t="str">
         <v/>
@@ -9604,19 +9604,19 @@
         <v/>
       </c>
       <c r="N111" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O111">
-        <v>0.19999999999999998</v>
+        <v>1</v>
       </c>
       <c r="P111" s="1" t="d">
         <v>2026-08-24T23:59:08.000Z</v>
       </c>
       <c r="Q111" s="1" t="d">
-        <v>2026-11-03T23:59:08.000Z</v>
+        <v>2026-08-25T23:59:08.000Z</v>
       </c>
       <c r="R111">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="S111" t="str">
         <v/>
@@ -9657,7 +9657,7 @@
         <v/>
       </c>
       <c r="D112" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -9687,19 +9687,19 @@
         <v/>
       </c>
       <c r="N112" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O112">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P112" s="1" t="d">
-        <v>2026-08-24T23:59:08.000Z</v>
+        <v>2026-08-25T23:59:08.000Z</v>
       </c>
       <c r="Q112" s="1" t="d">
         <v>2026-08-25T23:59:08.000Z</v>
       </c>
       <c r="R112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S112" t="str">
         <v/>
@@ -9740,13 +9740,13 @@
         <v/>
       </c>
       <c r="D113" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Mohammed Adel</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -9758,10 +9758,10 @@
         <v/>
       </c>
       <c r="J113" t="str">
-        <v>Mohammed Adel</v>
+        <v xml:space="preserve">Bshaier </v>
       </c>
       <c r="K113" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L113" t="str">
         <v/>
@@ -9770,10 +9770,10 @@
         <v/>
       </c>
       <c r="N113" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O113">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P113" s="1" t="d">
         <v>2026-08-25T23:59:08.000Z</v>
@@ -9782,7 +9782,7 @@
         <v>2026-08-25T23:59:08.000Z</v>
       </c>
       <c r="R113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S113" t="str">
         <v/>
@@ -9823,13 +9823,13 @@
         <v/>
       </c>
       <c r="D114" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -9841,10 +9841,10 @@
         <v/>
       </c>
       <c r="J114" t="str">
-        <v xml:space="preserve">Bshaier </v>
+        <v>Faisal Aljallali</v>
       </c>
       <c r="K114" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L114" t="str">
         <v/>
@@ -9859,13 +9859,13 @@
         <v>0</v>
       </c>
       <c r="P114" s="1" t="d">
-        <v>2026-08-25T23:59:08.000Z</v>
+        <v>2026-10-03T23:59:08.000Z</v>
       </c>
       <c r="Q114" s="1" t="d">
-        <v>2026-08-25T23:59:08.000Z</v>
+        <v>2026-10-28T23:59:08.000Z</v>
       </c>
       <c r="R114">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="S114" t="str">
         <v/>
@@ -9906,7 +9906,7 @@
         <v/>
       </c>
       <c r="D115" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -9927,7 +9927,7 @@
         <v>Faisal Aljallali</v>
       </c>
       <c r="K115" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L115" t="str">
         <v/>
@@ -9942,13 +9942,13 @@
         <v>0</v>
       </c>
       <c r="P115" s="1" t="d">
-        <v>2026-10-03T23:59:08.000Z</v>
+        <v>2026-10-31T23:59:08.000Z</v>
       </c>
       <c r="Q115" s="1" t="d">
-        <v>2026-10-28T23:59:08.000Z</v>
+        <v>2026-10-31T23:59:08.000Z</v>
       </c>
       <c r="R115">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="S115" t="str">
         <v/>
@@ -9989,7 +9989,7 @@
         <v/>
       </c>
       <c r="D116" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -10010,7 +10010,7 @@
         <v>Faisal Aljallali</v>
       </c>
       <c r="K116" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L116" t="str">
         <v/>
@@ -10025,13 +10025,13 @@
         <v>0</v>
       </c>
       <c r="P116" s="1" t="d">
-        <v>2026-10-31T23:59:08.000Z</v>
+        <v>2026-11-03T23:59:08.000Z</v>
       </c>
       <c r="Q116" s="1" t="d">
-        <v>2026-10-31T23:59:08.000Z</v>
+        <v>2026-11-10T23:59:08.000Z</v>
       </c>
       <c r="R116">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S116" t="str">
         <v/>
@@ -10063,22 +10063,22 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v/>
+        <v>RPA-016</v>
       </c>
       <c r="B117" t="str">
-        <v/>
-      </c>
-      <c r="C117" t="str">
-        <v/>
+        <v>Onboarding Documents</v>
+      </c>
+      <c r="C117">
+        <v>13440</v>
       </c>
       <c r="D117" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E117" t="str">
-        <v/>
+        <v>HR</v>
       </c>
       <c r="F117" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Anas </v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -10090,10 +10090,10 @@
         <v/>
       </c>
       <c r="J117" t="str">
-        <v>Faisal Aljallali</v>
+        <v xml:space="preserve">Anas </v>
       </c>
       <c r="K117" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L117" t="str">
         <v/>
@@ -10102,19 +10102,19 @@
         <v/>
       </c>
       <c r="N117" t="str">
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="P117" s="1" t="d">
-        <v>2026-11-03T23:59:08.000Z</v>
+        <v>2026-08-26T23:59:08.000Z</v>
       </c>
       <c r="Q117" s="1" t="d">
-        <v>2026-11-03T23:59:08.000Z</v>
+        <v>2026-11-09T23:59:08.000Z</v>
       </c>
       <c r="R117">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="S117" t="str">
         <v/>
@@ -10146,22 +10146,22 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>RPA-016</v>
+        <v/>
       </c>
       <c r="B118" t="str">
-        <v>Onboarding Documents</v>
-      </c>
-      <c r="C118">
-        <v>13440</v>
+        <v/>
+      </c>
+      <c r="C118" t="str">
+        <v/>
       </c>
       <c r="D118" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E118" t="str">
-        <v>HR</v>
+        <v/>
       </c>
       <c r="F118" t="str">
-        <v xml:space="preserve">Anas </v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -10173,10 +10173,10 @@
         <v/>
       </c>
       <c r="J118" t="str">
-        <v xml:space="preserve">Anas </v>
+        <v>Waleed Hamza</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L118" t="str">
         <v/>
@@ -10185,19 +10185,19 @@
         <v/>
       </c>
       <c r="N118" t="str">
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="O118">
-        <v>0.19999999999999998</v>
+        <v>1</v>
       </c>
       <c r="P118" s="1" t="d">
         <v>2026-08-26T23:59:08.000Z</v>
       </c>
       <c r="Q118" s="1" t="d">
-        <v>2026-11-02T23:59:08.000Z</v>
+        <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="R118">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="S118" t="str">
         <v/>
@@ -10238,7 +10238,7 @@
         <v/>
       </c>
       <c r="D119" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -10268,19 +10268,19 @@
         <v/>
       </c>
       <c r="N119" t="str">
-        <v>Completed</v>
+        <v>In Progress</v>
       </c>
       <c r="O119">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P119" s="1" t="d">
-        <v>2026-08-26T23:59:08.000Z</v>
+        <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="Q119" s="1" t="d">
         <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="R119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S119" t="str">
         <v/>
@@ -10321,13 +10321,13 @@
         <v/>
       </c>
       <c r="D120" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Waleed Hamza</v>
+        <v xml:space="preserve">Anas </v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -10339,10 +10339,10 @@
         <v/>
       </c>
       <c r="J120" t="str">
-        <v>Waleed Hamza</v>
+        <v xml:space="preserve">Anas </v>
       </c>
       <c r="K120" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L120" t="str">
         <v/>
@@ -10351,10 +10351,10 @@
         <v/>
       </c>
       <c r="N120" t="str">
-        <v>In Progress</v>
+        <v>Not Started</v>
       </c>
       <c r="O120">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P120" s="1" t="d">
         <v>2026-08-29T23:59:08.000Z</v>
@@ -10363,7 +10363,7 @@
         <v>2026-08-29T23:59:08.000Z</v>
       </c>
       <c r="R120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S120" t="str">
         <v/>
@@ -10404,13 +10404,13 @@
         <v/>
       </c>
       <c r="D121" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v xml:space="preserve">Anas </v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -10422,10 +10422,10 @@
         <v/>
       </c>
       <c r="J121" t="str">
-        <v xml:space="preserve">Anas </v>
+        <v>Hussain Khubrany</v>
       </c>
       <c r="K121" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L121" t="str">
         <v/>
@@ -10440,13 +10440,13 @@
         <v>0</v>
       </c>
       <c r="P121" s="1" t="d">
-        <v>2026-08-29T23:59:08.000Z</v>
+        <v>2026-10-06T23:59:08.000Z</v>
       </c>
       <c r="Q121" s="1" t="d">
-        <v>2026-08-29T23:59:08.000Z</v>
+        <v>2026-10-26T23:59:08.000Z</v>
       </c>
       <c r="R121">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S121" t="str">
         <v/>
@@ -10487,7 +10487,7 @@
         <v/>
       </c>
       <c r="D122" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -10508,7 +10508,7 @@
         <v>Hussain Khubrany</v>
       </c>
       <c r="K122" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L122" t="str">
         <v/>
@@ -10523,13 +10523,13 @@
         <v>0</v>
       </c>
       <c r="P122" s="1" t="d">
-        <v>2026-10-06T23:59:08.000Z</v>
+        <v>2026-10-28T23:59:08.000Z</v>
       </c>
       <c r="Q122" s="1" t="d">
-        <v>2026-10-26T23:59:08.000Z</v>
+        <v>2026-10-28T23:59:08.000Z</v>
       </c>
       <c r="R122">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S122" t="str">
         <v/>
@@ -10570,7 +10570,7 @@
         <v/>
       </c>
       <c r="D123" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -10591,7 +10591,7 @@
         <v>Hussain Khubrany</v>
       </c>
       <c r="K123" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L123" t="str">
         <v/>
@@ -10606,13 +10606,13 @@
         <v>0</v>
       </c>
       <c r="P123" s="1" t="d">
-        <v>2026-10-28T23:59:08.000Z</v>
+        <v>2026-11-02T23:59:08.000Z</v>
       </c>
       <c r="Q123" s="1" t="d">
-        <v>2026-10-28T23:59:08.000Z</v>
+        <v>2026-11-09T23:59:08.000Z</v>
       </c>
       <c r="R123">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S123" t="str">
         <v/>
@@ -10644,22 +10644,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v/>
+        <v>RPA-017</v>
       </c>
       <c r="B124" t="str">
-        <v/>
+        <v>MEDIUM</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Hussain Khubrany</v>
+        <v/>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -10671,10 +10671,10 @@
         <v/>
       </c>
       <c r="J124" t="str">
-        <v>Hussain Khubrany</v>
+        <v/>
       </c>
       <c r="K124" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L124" t="str">
         <v/>
@@ -10689,13 +10689,13 @@
         <v>0</v>
       </c>
       <c r="P124" s="1" t="d">
-        <v>2026-11-02T23:59:08.000Z</v>
+        <v>2026-09-27T23:59:08.000Z</v>
       </c>
       <c r="Q124" s="1" t="d">
-        <v>2026-11-02T23:59:08.000Z</v>
+        <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="R124">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S124" t="str">
         <v/>
@@ -10727,16 +10727,16 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>RPA-017</v>
+        <v/>
       </c>
       <c r="B125" t="str">
-        <v>MEDIUM</v>
+        <v/>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -10757,7 +10757,7 @@
         <v/>
       </c>
       <c r="K125" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L125" t="str">
         <v/>
@@ -10775,10 +10775,10 @@
         <v>2026-09-27T23:59:08.000Z</v>
       </c>
       <c r="Q125" s="1" t="d">
-        <v>2026-10-25T23:59:08.000Z</v>
+        <v>2026-09-28T23:59:08.000Z</v>
       </c>
       <c r="R125">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S125" t="str">
         <v/>
@@ -10790,7 +10790,7 @@
         <v>0</v>
       </c>
       <c r="V125" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W125" t="str">
         <v>No</v>
@@ -10819,7 +10819,7 @@
         <v/>
       </c>
       <c r="D126" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -10854,14 +10854,14 @@
       <c r="O126">
         <v>0</v>
       </c>
-      <c r="P126" s="1" t="d">
-        <v>2026-09-27T23:59:08.000Z</v>
-      </c>
-      <c r="Q126" s="1" t="d">
-        <v>2026-09-28T23:59:08.000Z</v>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
       </c>
       <c r="R126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S126" t="str">
         <v/>
@@ -10902,7 +10902,7 @@
         <v/>
       </c>
       <c r="D127" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -10923,7 +10923,7 @@
         <v/>
       </c>
       <c r="K127" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L127" t="str">
         <v/>
@@ -10985,7 +10985,7 @@
         <v/>
       </c>
       <c r="D128" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -11006,7 +11006,7 @@
         <v/>
       </c>
       <c r="K128" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L128" t="str">
         <v/>
@@ -11020,14 +11020,14 @@
       <c r="O128">
         <v>0</v>
       </c>
-      <c r="P128" t="str">
-        <v/>
-      </c>
-      <c r="Q128" t="str">
-        <v/>
+      <c r="P128" s="1" t="d">
+        <v>2026-10-06T23:59:08.000Z</v>
+      </c>
+      <c r="Q128" s="1" t="d">
+        <v>2026-10-19T23:59:08.000Z</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S128" t="str">
         <v/>
@@ -11068,7 +11068,7 @@
         <v/>
       </c>
       <c r="D129" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -11089,7 +11089,7 @@
         <v/>
       </c>
       <c r="K129" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L129" t="str">
         <v/>
@@ -11104,13 +11104,13 @@
         <v>0</v>
       </c>
       <c r="P129" s="1" t="d">
-        <v>2026-10-06T23:59:08.000Z</v>
+        <v>2026-10-20T23:59:08.000Z</v>
       </c>
       <c r="Q129" s="1" t="d">
-        <v>2026-10-19T23:59:08.000Z</v>
+        <v>2026-10-20T23:59:08.000Z</v>
       </c>
       <c r="R129">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S129" t="str">
         <v/>
@@ -11151,7 +11151,7 @@
         <v/>
       </c>
       <c r="D130" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -11172,7 +11172,7 @@
         <v/>
       </c>
       <c r="K130" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L130" t="str">
         <v/>
@@ -11187,13 +11187,13 @@
         <v>0</v>
       </c>
       <c r="P130" s="1" t="d">
-        <v>2026-10-20T23:59:08.000Z</v>
+        <v>2026-10-25T23:59:08.000Z</v>
       </c>
       <c r="Q130" s="1" t="d">
-        <v>2026-10-20T23:59:08.000Z</v>
+        <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="R130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S130" t="str">
         <v/>
@@ -11225,16 +11225,16 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v/>
+        <v>RPA-018</v>
       </c>
       <c r="B131" t="str">
-        <v/>
+        <v>MEDIUM</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -11255,7 +11255,7 @@
         <v/>
       </c>
       <c r="K131" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L131" t="str">
         <v/>
@@ -11270,13 +11270,13 @@
         <v>0</v>
       </c>
       <c r="P131" s="1" t="d">
-        <v>2026-10-25T23:59:08.000Z</v>
+        <v>2026-09-27T23:59:08.000Z</v>
       </c>
       <c r="Q131" s="1" t="d">
-        <v>2026-10-25T23:59:08.000Z</v>
+        <v>2026-11-03T23:59:08.000Z</v>
       </c>
       <c r="R131">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S131" t="str">
         <v/>
@@ -11288,7 +11288,7 @@
         <v>0</v>
       </c>
       <c r="V131" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W131" t="str">
         <v>No</v>
@@ -11308,16 +11308,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>RPA-018</v>
+        <v/>
       </c>
       <c r="B132" t="str">
-        <v>MEDIUM</v>
+        <v/>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -11338,7 +11338,7 @@
         <v/>
       </c>
       <c r="K132" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L132" t="str">
         <v/>
@@ -11356,10 +11356,10 @@
         <v>2026-09-27T23:59:08.000Z</v>
       </c>
       <c r="Q132" s="1" t="d">
-        <v>2026-11-01T23:59:08.000Z</v>
+        <v>2026-09-28T23:59:08.000Z</v>
       </c>
       <c r="R132">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S132" t="str">
         <v/>
@@ -11371,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="V132" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W132" t="str">
         <v>No</v>
@@ -11400,7 +11400,7 @@
         <v/>
       </c>
       <c r="D133" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -11435,14 +11435,14 @@
       <c r="O133">
         <v>0</v>
       </c>
-      <c r="P133" s="1" t="d">
-        <v>2026-09-27T23:59:08.000Z</v>
-      </c>
-      <c r="Q133" s="1" t="d">
-        <v>2026-09-28T23:59:08.000Z</v>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
       </c>
       <c r="R133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S133" t="str">
         <v/>
@@ -11483,7 +11483,7 @@
         <v/>
       </c>
       <c r="D134" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -11504,7 +11504,7 @@
         <v/>
       </c>
       <c r="K134" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L134" t="str">
         <v/>
@@ -11566,7 +11566,7 @@
         <v/>
       </c>
       <c r="D135" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -11587,7 +11587,7 @@
         <v/>
       </c>
       <c r="K135" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L135" t="str">
         <v/>
@@ -11601,14 +11601,14 @@
       <c r="O135">
         <v>0</v>
       </c>
-      <c r="P135" t="str">
-        <v/>
-      </c>
-      <c r="Q135" t="str">
-        <v/>
+      <c r="P135" s="1" t="d">
+        <v>2026-10-13T23:59:08.000Z</v>
+      </c>
+      <c r="Q135" s="1" t="d">
+        <v>2026-10-26T23:59:08.000Z</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S135" t="str">
         <v/>
@@ -11649,7 +11649,7 @@
         <v/>
       </c>
       <c r="D136" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -11670,7 +11670,7 @@
         <v/>
       </c>
       <c r="K136" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L136" t="str">
         <v/>
@@ -11685,13 +11685,13 @@
         <v>0</v>
       </c>
       <c r="P136" s="1" t="d">
-        <v>2026-10-13T23:59:08.000Z</v>
+        <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="Q136" s="1" t="d">
-        <v>2026-10-26T23:59:08.000Z</v>
+        <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="R136">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S136" t="str">
         <v/>
@@ -11732,7 +11732,7 @@
         <v/>
       </c>
       <c r="D137" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -11753,7 +11753,7 @@
         <v/>
       </c>
       <c r="K137" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L137" t="str">
         <v/>
@@ -11768,13 +11768,13 @@
         <v>0</v>
       </c>
       <c r="P137" s="1" t="d">
-        <v>2026-10-27T23:59:08.000Z</v>
+        <v>2026-11-01T23:59:08.000Z</v>
       </c>
       <c r="Q137" s="1" t="d">
-        <v>2026-10-27T23:59:08.000Z</v>
+        <v>2026-11-03T23:59:08.000Z</v>
       </c>
       <c r="R137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S137" t="str">
         <v/>
@@ -11806,16 +11806,16 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v/>
+        <v>RPA-019</v>
       </c>
       <c r="B138" t="str">
-        <v/>
+        <v>MEDIUM</v>
       </c>
       <c r="C138" t="str">
         <v/>
       </c>
       <c r="D138" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -11836,7 +11836,7 @@
         <v/>
       </c>
       <c r="K138" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L138" t="str">
         <v/>
@@ -11851,13 +11851,13 @@
         <v>0</v>
       </c>
       <c r="P138" s="1" t="d">
-        <v>2026-11-01T23:59:08.000Z</v>
+        <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="Q138" s="1" t="d">
-        <v>2026-11-01T23:59:08.000Z</v>
+        <v>2026-11-21T23:59:08.000Z</v>
       </c>
       <c r="R138">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S138" t="str">
         <v/>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="V138" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W138" t="str">
         <v>No</v>
@@ -11889,16 +11889,16 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>RPA-019</v>
+        <v/>
       </c>
       <c r="B139" t="str">
-        <v>MEDIUM</v>
+        <v/>
       </c>
       <c r="C139" t="str">
         <v/>
       </c>
       <c r="D139" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -11919,7 +11919,7 @@
         <v/>
       </c>
       <c r="K139" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L139" t="str">
         <v/>
@@ -11937,10 +11937,10 @@
         <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="Q139" s="1" t="d">
-        <v>2026-11-17T23:59:08.000Z</v>
+        <v>2026-10-28T23:59:08.000Z</v>
       </c>
       <c r="R139">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S139" t="str">
         <v/>
@@ -11952,7 +11952,7 @@
         <v>0</v>
       </c>
       <c r="V139" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W139" t="str">
         <v>No</v>
@@ -11981,7 +11981,7 @@
         <v/>
       </c>
       <c r="D140" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -12016,14 +12016,14 @@
       <c r="O140">
         <v>0</v>
       </c>
-      <c r="P140" s="1" t="d">
-        <v>2026-10-27T23:59:08.000Z</v>
-      </c>
-      <c r="Q140" s="1" t="d">
-        <v>2026-10-28T23:59:08.000Z</v>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
       </c>
       <c r="R140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S140" t="str">
         <v/>
@@ -12064,7 +12064,7 @@
         <v/>
       </c>
       <c r="D141" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -12085,7 +12085,7 @@
         <v/>
       </c>
       <c r="K141" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L141" t="str">
         <v/>
@@ -12147,7 +12147,7 @@
         <v/>
       </c>
       <c r="D142" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -12168,7 +12168,7 @@
         <v/>
       </c>
       <c r="K142" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L142" t="str">
         <v/>
@@ -12182,14 +12182,14 @@
       <c r="O142">
         <v>0</v>
       </c>
-      <c r="P142" t="str">
-        <v/>
-      </c>
-      <c r="Q142" t="str">
-        <v/>
+      <c r="P142" s="1" t="d">
+        <v>2026-10-31T23:59:08.000Z</v>
+      </c>
+      <c r="Q142" s="1" t="d">
+        <v>2026-11-11T23:59:08.000Z</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S142" t="str">
         <v/>
@@ -12230,7 +12230,7 @@
         <v/>
       </c>
       <c r="D143" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -12251,7 +12251,7 @@
         <v/>
       </c>
       <c r="K143" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L143" t="str">
         <v/>
@@ -12266,13 +12266,13 @@
         <v>0</v>
       </c>
       <c r="P143" s="1" t="d">
-        <v>2026-10-31T23:59:08.000Z</v>
+        <v>2026-11-14T23:59:08.000Z</v>
       </c>
       <c r="Q143" s="1" t="d">
-        <v>2026-11-11T23:59:08.000Z</v>
+        <v>2026-11-14T23:59:08.000Z</v>
       </c>
       <c r="R143">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S143" t="str">
         <v/>
@@ -12313,7 +12313,7 @@
         <v/>
       </c>
       <c r="D144" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -12334,7 +12334,7 @@
         <v/>
       </c>
       <c r="K144" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L144" t="str">
         <v/>
@@ -12349,13 +12349,13 @@
         <v>0</v>
       </c>
       <c r="P144" s="1" t="d">
-        <v>2026-11-14T23:59:08.000Z</v>
+        <v>2026-11-17T23:59:08.000Z</v>
       </c>
       <c r="Q144" s="1" t="d">
-        <v>2026-11-14T23:59:08.000Z</v>
+        <v>2026-11-21T23:59:08.000Z</v>
       </c>
       <c r="R144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S144" t="str">
         <v/>
@@ -12387,16 +12387,16 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v/>
+        <v>RPA-020</v>
       </c>
       <c r="B145" t="str">
-        <v/>
+        <v>MEDIUM</v>
       </c>
       <c r="C145" t="str">
         <v/>
       </c>
       <c r="D145" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -12417,7 +12417,7 @@
         <v/>
       </c>
       <c r="K145" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L145" t="str">
         <v/>
@@ -12432,13 +12432,13 @@
         <v>0</v>
       </c>
       <c r="P145" s="1" t="d">
-        <v>2026-11-17T23:59:08.000Z</v>
+        <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="Q145" s="1" t="d">
-        <v>2026-11-17T23:59:08.000Z</v>
+        <v>2026-11-21T23:59:08.000Z</v>
       </c>
       <c r="R145">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S145" t="str">
         <v/>
@@ -12450,7 +12450,7 @@
         <v>0</v>
       </c>
       <c r="V145" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W145" t="str">
         <v>No</v>
@@ -12470,16 +12470,16 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>RPA-020</v>
+        <v/>
       </c>
       <c r="B146" t="str">
-        <v>MEDIUM</v>
+        <v/>
       </c>
       <c r="C146" t="str">
         <v/>
       </c>
       <c r="D146" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -12500,7 +12500,7 @@
         <v/>
       </c>
       <c r="K146" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L146" t="str">
         <v/>
@@ -12518,10 +12518,10 @@
         <v>2026-10-27T23:59:08.000Z</v>
       </c>
       <c r="Q146" s="1" t="d">
-        <v>2026-11-17T23:59:08.000Z</v>
+        <v>2026-10-28T23:59:08.000Z</v>
       </c>
       <c r="R146">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S146" t="str">
         <v/>
@@ -12533,7 +12533,7 @@
         <v>0</v>
       </c>
       <c r="V146" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W146" t="str">
         <v>No</v>
@@ -12562,7 +12562,7 @@
         <v/>
       </c>
       <c r="D147" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -12597,14 +12597,14 @@
       <c r="O147">
         <v>0</v>
       </c>
-      <c r="P147" s="1" t="d">
-        <v>2026-10-27T23:59:08.000Z</v>
-      </c>
-      <c r="Q147" s="1" t="d">
-        <v>2026-10-28T23:59:08.000Z</v>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
       </c>
       <c r="R147">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S147" t="str">
         <v/>
@@ -12645,7 +12645,7 @@
         <v/>
       </c>
       <c r="D148" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -12666,7 +12666,7 @@
         <v/>
       </c>
       <c r="K148" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L148" t="str">
         <v/>
@@ -12728,7 +12728,7 @@
         <v/>
       </c>
       <c r="D149" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -12749,7 +12749,7 @@
         <v/>
       </c>
       <c r="K149" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L149" t="str">
         <v/>
@@ -12763,14 +12763,14 @@
       <c r="O149">
         <v>0</v>
       </c>
-      <c r="P149" t="str">
-        <v/>
-      </c>
-      <c r="Q149" t="str">
-        <v/>
+      <c r="P149" s="1" t="d">
+        <v>2026-10-31T23:59:08.000Z</v>
+      </c>
+      <c r="Q149" s="1" t="d">
+        <v>2026-11-11T23:59:08.000Z</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S149" t="str">
         <v/>
@@ -12811,7 +12811,7 @@
         <v/>
       </c>
       <c r="D150" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -12832,7 +12832,7 @@
         <v/>
       </c>
       <c r="K150" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L150" t="str">
         <v/>
@@ -12847,13 +12847,13 @@
         <v>0</v>
       </c>
       <c r="P150" s="1" t="d">
-        <v>2026-10-31T23:59:08.000Z</v>
+        <v>2026-11-14T23:59:08.000Z</v>
       </c>
       <c r="Q150" s="1" t="d">
-        <v>2026-11-11T23:59:08.000Z</v>
+        <v>2026-11-14T23:59:08.000Z</v>
       </c>
       <c r="R150">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S150" t="str">
         <v/>
@@ -12894,7 +12894,7 @@
         <v/>
       </c>
       <c r="D151" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -12915,7 +12915,7 @@
         <v/>
       </c>
       <c r="K151" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L151" t="str">
         <v/>
@@ -12930,13 +12930,13 @@
         <v>0</v>
       </c>
       <c r="P151" s="1" t="d">
-        <v>2026-11-14T23:59:08.000Z</v>
+        <v>2026-11-17T23:59:08.000Z</v>
       </c>
       <c r="Q151" s="1" t="d">
-        <v>2026-11-14T23:59:08.000Z</v>
+        <v>2026-11-21T23:59:08.000Z</v>
       </c>
       <c r="R151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S151" t="str">
         <v/>
@@ -12968,16 +12968,16 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v/>
+        <v>RPA-021</v>
       </c>
       <c r="B152" t="str">
-        <v/>
+        <v>MEDIUM</v>
       </c>
       <c r="C152" t="str">
         <v/>
       </c>
       <c r="D152" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -12998,7 +12998,7 @@
         <v/>
       </c>
       <c r="K152" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L152" t="str">
         <v/>
@@ -13013,13 +13013,13 @@
         <v>0</v>
       </c>
       <c r="P152" s="1" t="d">
-        <v>2026-11-17T23:59:08.000Z</v>
+        <v>2026-11-28T23:59:08.000Z</v>
       </c>
       <c r="Q152" s="1" t="d">
-        <v>2026-11-17T23:59:08.000Z</v>
+        <v>2026-12-21T23:59:08.000Z</v>
       </c>
       <c r="R152">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S152" t="str">
         <v/>
@@ -13031,7 +13031,7 @@
         <v>0</v>
       </c>
       <c r="V152" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W152" t="str">
         <v>No</v>
@@ -13051,16 +13051,16 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>RPA-021</v>
+        <v/>
       </c>
       <c r="B153" t="str">
-        <v>MEDIUM</v>
+        <v/>
       </c>
       <c r="C153" t="str">
         <v/>
       </c>
       <c r="D153" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -13081,7 +13081,7 @@
         <v/>
       </c>
       <c r="K153" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L153" t="str">
         <v/>
@@ -13099,10 +13099,10 @@
         <v>2026-11-28T23:59:08.000Z</v>
       </c>
       <c r="Q153" s="1" t="d">
-        <v>2026-12-19T23:59:08.000Z</v>
+        <v>2026-11-29T23:59:08.000Z</v>
       </c>
       <c r="R153">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S153" t="str">
         <v/>
@@ -13114,7 +13114,7 @@
         <v>0</v>
       </c>
       <c r="V153" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W153" t="str">
         <v>No</v>
@@ -13143,7 +13143,7 @@
         <v/>
       </c>
       <c r="D154" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -13178,14 +13178,14 @@
       <c r="O154">
         <v>0</v>
       </c>
-      <c r="P154" s="1" t="d">
-        <v>2026-11-28T23:59:08.000Z</v>
-      </c>
-      <c r="Q154" s="1" t="d">
-        <v>2026-11-29T23:59:08.000Z</v>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
       </c>
       <c r="R154">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S154" t="str">
         <v/>
@@ -13226,7 +13226,7 @@
         <v/>
       </c>
       <c r="D155" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -13247,7 +13247,7 @@
         <v/>
       </c>
       <c r="K155" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L155" t="str">
         <v/>
@@ -13309,7 +13309,7 @@
         <v/>
       </c>
       <c r="D156" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -13330,7 +13330,7 @@
         <v/>
       </c>
       <c r="K156" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L156" t="str">
         <v/>
@@ -13344,14 +13344,14 @@
       <c r="O156">
         <v>0</v>
       </c>
-      <c r="P156" t="str">
-        <v/>
-      </c>
-      <c r="Q156" t="str">
-        <v/>
+      <c r="P156" s="1" t="d">
+        <v>2026-11-30T23:59:08.000Z</v>
+      </c>
+      <c r="Q156" s="1" t="d">
+        <v>2026-12-13T23:59:08.000Z</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S156" t="str">
         <v/>
@@ -13392,7 +13392,7 @@
         <v/>
       </c>
       <c r="D157" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -13413,7 +13413,7 @@
         <v/>
       </c>
       <c r="K157" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L157" t="str">
         <v/>
@@ -13428,13 +13428,13 @@
         <v>0</v>
       </c>
       <c r="P157" s="1" t="d">
-        <v>2026-11-30T23:59:08.000Z</v>
+        <v>2026-12-14T23:59:08.000Z</v>
       </c>
       <c r="Q157" s="1" t="d">
-        <v>2026-12-13T23:59:08.000Z</v>
+        <v>2026-12-14T23:59:08.000Z</v>
       </c>
       <c r="R157">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S157" t="str">
         <v/>
@@ -13475,7 +13475,7 @@
         <v/>
       </c>
       <c r="D158" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -13496,7 +13496,7 @@
         <v/>
       </c>
       <c r="K158" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L158" t="str">
         <v/>
@@ -13511,13 +13511,13 @@
         <v>0</v>
       </c>
       <c r="P158" s="1" t="d">
-        <v>2026-12-14T23:59:08.000Z</v>
+        <v>2026-12-19T23:59:08.000Z</v>
       </c>
       <c r="Q158" s="1" t="d">
-        <v>2026-12-14T23:59:08.000Z</v>
+        <v>2026-12-21T23:59:08.000Z</v>
       </c>
       <c r="R158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S158" t="str">
         <v/>
@@ -13549,16 +13549,16 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v/>
+        <v>RPA-022</v>
       </c>
       <c r="B159" t="str">
-        <v/>
+        <v>LOW</v>
       </c>
       <c r="C159" t="str">
         <v/>
       </c>
       <c r="D159" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -13579,7 +13579,7 @@
         <v/>
       </c>
       <c r="K159" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L159" t="str">
         <v/>
@@ -13594,13 +13594,13 @@
         <v>0</v>
       </c>
       <c r="P159" s="1" t="d">
-        <v>2026-12-19T23:59:08.000Z</v>
+        <v>2026-11-28T23:59:08.000Z</v>
       </c>
       <c r="Q159" s="1" t="d">
-        <v>2026-12-19T23:59:08.000Z</v>
+        <v>2026-12-21T23:59:08.000Z</v>
       </c>
       <c r="R159">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S159" t="str">
         <v/>
@@ -13612,7 +13612,7 @@
         <v>0</v>
       </c>
       <c r="V159" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W159" t="str">
         <v>No</v>
@@ -13632,16 +13632,16 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>RPA-022</v>
+        <v/>
       </c>
       <c r="B160" t="str">
-        <v>LOW</v>
+        <v/>
       </c>
       <c r="C160" t="str">
         <v/>
       </c>
       <c r="D160" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -13662,7 +13662,7 @@
         <v/>
       </c>
       <c r="K160" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L160" t="str">
         <v/>
@@ -13680,10 +13680,10 @@
         <v>2026-11-28T23:59:08.000Z</v>
       </c>
       <c r="Q160" s="1" t="d">
-        <v>2026-12-19T23:59:08.000Z</v>
+        <v>2026-11-29T23:59:08.000Z</v>
       </c>
       <c r="R160">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S160" t="str">
         <v/>
@@ -13695,7 +13695,7 @@
         <v>0</v>
       </c>
       <c r="V160" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W160" t="str">
         <v>No</v>
@@ -13724,7 +13724,7 @@
         <v/>
       </c>
       <c r="D161" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -13759,14 +13759,14 @@
       <c r="O161">
         <v>0</v>
       </c>
-      <c r="P161" s="1" t="d">
-        <v>2026-11-28T23:59:08.000Z</v>
-      </c>
-      <c r="Q161" s="1" t="d">
-        <v>2026-11-29T23:59:08.000Z</v>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161" t="str">
+        <v/>
       </c>
       <c r="R161">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S161" t="str">
         <v/>
@@ -13807,7 +13807,7 @@
         <v/>
       </c>
       <c r="D162" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -13828,7 +13828,7 @@
         <v/>
       </c>
       <c r="K162" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L162" t="str">
         <v/>
@@ -13890,7 +13890,7 @@
         <v/>
       </c>
       <c r="D163" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -13911,7 +13911,7 @@
         <v/>
       </c>
       <c r="K163" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L163" t="str">
         <v/>
@@ -13925,14 +13925,14 @@
       <c r="O163">
         <v>0</v>
       </c>
-      <c r="P163" t="str">
-        <v/>
-      </c>
-      <c r="Q163" t="str">
-        <v/>
+      <c r="P163" s="1" t="d">
+        <v>2026-11-30T23:59:08.000Z</v>
+      </c>
+      <c r="Q163" s="1" t="d">
+        <v>2026-12-13T23:59:08.000Z</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S163" t="str">
         <v/>
@@ -13973,7 +13973,7 @@
         <v/>
       </c>
       <c r="D164" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -13994,7 +13994,7 @@
         <v/>
       </c>
       <c r="K164" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L164" t="str">
         <v/>
@@ -14009,13 +14009,13 @@
         <v>0</v>
       </c>
       <c r="P164" s="1" t="d">
-        <v>2026-11-30T23:59:08.000Z</v>
+        <v>2026-12-14T23:59:08.000Z</v>
       </c>
       <c r="Q164" s="1" t="d">
-        <v>2026-12-13T23:59:08.000Z</v>
+        <v>2026-12-14T23:59:08.000Z</v>
       </c>
       <c r="R164">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S164" t="str">
         <v/>
@@ -14056,7 +14056,7 @@
         <v/>
       </c>
       <c r="D165" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -14077,7 +14077,7 @@
         <v/>
       </c>
       <c r="K165" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L165" t="str">
         <v/>
@@ -14092,13 +14092,13 @@
         <v>0</v>
       </c>
       <c r="P165" s="1" t="d">
-        <v>2026-12-14T23:59:08.000Z</v>
+        <v>2026-12-19T23:59:08.000Z</v>
       </c>
       <c r="Q165" s="1" t="d">
-        <v>2026-12-14T23:59:08.000Z</v>
+        <v>2026-12-21T23:59:08.000Z</v>
       </c>
       <c r="R165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S165" t="str">
         <v/>
@@ -14130,16 +14130,16 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v/>
+        <v>RPA-023</v>
       </c>
       <c r="B166" t="str">
-        <v/>
+        <v>LOW</v>
       </c>
       <c r="C166" t="str">
         <v/>
       </c>
       <c r="D166" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -14160,7 +14160,7 @@
         <v/>
       </c>
       <c r="K166" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L166" t="str">
         <v/>
@@ -14175,13 +14175,13 @@
         <v>0</v>
       </c>
       <c r="P166" s="1" t="d">
-        <v>2026-12-19T23:59:08.000Z</v>
+        <v>2026-12-28T23:59:08.000Z</v>
       </c>
       <c r="Q166" s="1" t="d">
-        <v>2026-12-19T23:59:08.000Z</v>
+        <v>2027-01-20T23:59:08.000Z</v>
       </c>
       <c r="R166">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S166" t="str">
         <v/>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="V166" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W166" t="str">
         <v>No</v>
@@ -14213,16 +14213,16 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>RPA-023</v>
+        <v/>
       </c>
       <c r="B167" t="str">
-        <v>LOW</v>
+        <v/>
       </c>
       <c r="C167" t="str">
         <v/>
       </c>
       <c r="D167" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -14243,7 +14243,7 @@
         <v/>
       </c>
       <c r="K167" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L167" t="str">
         <v/>
@@ -14261,10 +14261,10 @@
         <v>2026-12-28T23:59:08.000Z</v>
       </c>
       <c r="Q167" s="1" t="d">
-        <v>2027-01-18T23:59:08.000Z</v>
+        <v>2026-12-29T23:59:08.000Z</v>
       </c>
       <c r="R167">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S167" t="str">
         <v/>
@@ -14276,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="V167" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W167" t="str">
         <v>No</v>
@@ -14305,7 +14305,7 @@
         <v/>
       </c>
       <c r="D168" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -14340,14 +14340,14 @@
       <c r="O168">
         <v>0</v>
       </c>
-      <c r="P168" s="1" t="d">
-        <v>2026-12-28T23:59:08.000Z</v>
-      </c>
-      <c r="Q168" s="1" t="d">
-        <v>2026-12-29T23:59:08.000Z</v>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
       </c>
       <c r="R168">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S168" t="str">
         <v/>
@@ -14388,7 +14388,7 @@
         <v/>
       </c>
       <c r="D169" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -14409,7 +14409,7 @@
         <v/>
       </c>
       <c r="K169" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L169" t="str">
         <v/>
@@ -14471,7 +14471,7 @@
         <v/>
       </c>
       <c r="D170" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -14492,7 +14492,7 @@
         <v/>
       </c>
       <c r="K170" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L170" t="str">
         <v/>
@@ -14506,14 +14506,14 @@
       <c r="O170">
         <v>0</v>
       </c>
-      <c r="P170" t="str">
-        <v/>
-      </c>
-      <c r="Q170" t="str">
-        <v/>
+      <c r="P170" s="1" t="d">
+        <v>2026-12-30T23:59:08.000Z</v>
+      </c>
+      <c r="Q170" s="1" t="d">
+        <v>2027-01-12T23:59:08.000Z</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S170" t="str">
         <v/>
@@ -14554,7 +14554,7 @@
         <v/>
       </c>
       <c r="D171" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -14575,7 +14575,7 @@
         <v/>
       </c>
       <c r="K171" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L171" t="str">
         <v/>
@@ -14590,13 +14590,13 @@
         <v>0</v>
       </c>
       <c r="P171" s="1" t="d">
-        <v>2026-12-30T23:59:08.000Z</v>
+        <v>2027-01-13T23:59:08.000Z</v>
       </c>
       <c r="Q171" s="1" t="d">
-        <v>2027-01-12T23:59:08.000Z</v>
+        <v>2027-01-13T23:59:08.000Z</v>
       </c>
       <c r="R171">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S171" t="str">
         <v/>
@@ -14637,7 +14637,7 @@
         <v/>
       </c>
       <c r="D172" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -14658,7 +14658,7 @@
         <v/>
       </c>
       <c r="K172" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L172" t="str">
         <v/>
@@ -14673,13 +14673,13 @@
         <v>0</v>
       </c>
       <c r="P172" s="1" t="d">
-        <v>2027-01-13T23:59:08.000Z</v>
+        <v>2027-01-18T23:59:08.000Z</v>
       </c>
       <c r="Q172" s="1" t="d">
-        <v>2027-01-13T23:59:08.000Z</v>
+        <v>2027-01-20T23:59:08.000Z</v>
       </c>
       <c r="R172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S172" t="str">
         <v/>
@@ -14711,16 +14711,16 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v/>
+        <v>RPA-024</v>
       </c>
       <c r="B173" t="str">
-        <v/>
+        <v>LOW</v>
       </c>
       <c r="C173" t="str">
         <v/>
       </c>
       <c r="D173" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -14741,7 +14741,7 @@
         <v/>
       </c>
       <c r="K173" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L173" t="str">
         <v/>
@@ -14756,13 +14756,13 @@
         <v>0</v>
       </c>
       <c r="P173" s="1" t="d">
-        <v>2027-01-18T23:59:08.000Z</v>
+        <v>2026-12-28T23:59:08.000Z</v>
       </c>
       <c r="Q173" s="1" t="d">
-        <v>2027-01-18T23:59:08.000Z</v>
+        <v>2027-01-20T23:59:08.000Z</v>
       </c>
       <c r="R173">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S173" t="str">
         <v/>
@@ -14774,7 +14774,7 @@
         <v>0</v>
       </c>
       <c r="V173" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W173" t="str">
         <v>No</v>
@@ -14794,16 +14794,16 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>RPA-024</v>
+        <v/>
       </c>
       <c r="B174" t="str">
-        <v>LOW</v>
+        <v/>
       </c>
       <c r="C174" t="str">
         <v/>
       </c>
       <c r="D174" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -14824,7 +14824,7 @@
         <v/>
       </c>
       <c r="K174" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L174" t="str">
         <v/>
@@ -14842,10 +14842,10 @@
         <v>2026-12-28T23:59:08.000Z</v>
       </c>
       <c r="Q174" s="1" t="d">
-        <v>2027-01-18T23:59:08.000Z</v>
+        <v>2026-12-29T23:59:08.000Z</v>
       </c>
       <c r="R174">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S174" t="str">
         <v/>
@@ -14857,7 +14857,7 @@
         <v>0</v>
       </c>
       <c r="V174" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W174" t="str">
         <v>No</v>
@@ -14886,7 +14886,7 @@
         <v/>
       </c>
       <c r="D175" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -14921,14 +14921,14 @@
       <c r="O175">
         <v>0</v>
       </c>
-      <c r="P175" s="1" t="d">
-        <v>2026-12-28T23:59:08.000Z</v>
-      </c>
-      <c r="Q175" s="1" t="d">
-        <v>2026-12-29T23:59:08.000Z</v>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
       </c>
       <c r="R175">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S175" t="str">
         <v/>
@@ -14969,7 +14969,7 @@
         <v/>
       </c>
       <c r="D176" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -14990,7 +14990,7 @@
         <v/>
       </c>
       <c r="K176" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L176" t="str">
         <v/>
@@ -15052,7 +15052,7 @@
         <v/>
       </c>
       <c r="D177" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -15073,7 +15073,7 @@
         <v/>
       </c>
       <c r="K177" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L177" t="str">
         <v/>
@@ -15087,14 +15087,14 @@
       <c r="O177">
         <v>0</v>
       </c>
-      <c r="P177" t="str">
-        <v/>
-      </c>
-      <c r="Q177" t="str">
-        <v/>
+      <c r="P177" s="1" t="d">
+        <v>2026-12-30T23:59:08.000Z</v>
+      </c>
+      <c r="Q177" s="1" t="d">
+        <v>2027-01-12T23:59:08.000Z</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S177" t="str">
         <v/>
@@ -15135,7 +15135,7 @@
         <v/>
       </c>
       <c r="D178" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -15156,7 +15156,7 @@
         <v/>
       </c>
       <c r="K178" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L178" t="str">
         <v/>
@@ -15171,13 +15171,13 @@
         <v>0</v>
       </c>
       <c r="P178" s="1" t="d">
-        <v>2026-12-30T23:59:08.000Z</v>
+        <v>2027-01-13T23:59:08.000Z</v>
       </c>
       <c r="Q178" s="1" t="d">
-        <v>2027-01-12T23:59:08.000Z</v>
+        <v>2027-01-13T23:59:08.000Z</v>
       </c>
       <c r="R178">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S178" t="str">
         <v/>
@@ -15218,7 +15218,7 @@
         <v/>
       </c>
       <c r="D179" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -15239,7 +15239,7 @@
         <v/>
       </c>
       <c r="K179" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L179" t="str">
         <v/>
@@ -15254,13 +15254,13 @@
         <v>0</v>
       </c>
       <c r="P179" s="1" t="d">
-        <v>2027-01-13T23:59:08.000Z</v>
+        <v>2027-01-18T23:59:08.000Z</v>
       </c>
       <c r="Q179" s="1" t="d">
-        <v>2027-01-13T23:59:08.000Z</v>
+        <v>2027-01-20T23:59:08.000Z</v>
       </c>
       <c r="R179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S179" t="str">
         <v/>
@@ -15292,16 +15292,16 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v/>
+        <v>RPA-025</v>
       </c>
       <c r="B180" t="str">
-        <v/>
+        <v>LOW</v>
       </c>
       <c r="C180" t="str">
         <v/>
       </c>
       <c r="D180" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -15322,7 +15322,7 @@
         <v/>
       </c>
       <c r="K180" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L180" t="str">
         <v/>
@@ -15337,13 +15337,13 @@
         <v>0</v>
       </c>
       <c r="P180" s="1" t="d">
-        <v>2027-01-18T23:59:08.000Z</v>
+        <v>2027-01-27T23:59:08.000Z</v>
       </c>
       <c r="Q180" s="1" t="d">
-        <v>2027-01-18T23:59:08.000Z</v>
+        <v>2027-02-21T23:59:08.000Z</v>
       </c>
       <c r="R180">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S180" t="str">
         <v/>
@@ -15355,7 +15355,7 @@
         <v>0</v>
       </c>
       <c r="V180" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W180" t="str">
         <v>No</v>
@@ -15375,16 +15375,16 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>RPA-025</v>
+        <v/>
       </c>
       <c r="B181" t="str">
-        <v>LOW</v>
+        <v/>
       </c>
       <c r="C181" t="str">
         <v/>
       </c>
       <c r="D181" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -15405,7 +15405,7 @@
         <v/>
       </c>
       <c r="K181" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L181" t="str">
         <v/>
@@ -15423,10 +15423,10 @@
         <v>2027-01-27T23:59:08.000Z</v>
       </c>
       <c r="Q181" s="1" t="d">
-        <v>2027-02-17T23:59:08.000Z</v>
+        <v>2027-01-30T23:59:08.000Z</v>
       </c>
       <c r="R181">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S181" t="str">
         <v/>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="V181" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W181" t="str">
         <v>No</v>
@@ -15467,7 +15467,7 @@
         <v/>
       </c>
       <c r="D182" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -15502,14 +15502,14 @@
       <c r="O182">
         <v>0</v>
       </c>
-      <c r="P182" s="1" t="d">
-        <v>2027-01-27T23:59:08.000Z</v>
-      </c>
-      <c r="Q182" s="1" t="d">
-        <v>2027-01-30T23:59:08.000Z</v>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
       </c>
       <c r="R182">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S182" t="str">
         <v/>
@@ -15550,7 +15550,7 @@
         <v/>
       </c>
       <c r="D183" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -15571,7 +15571,7 @@
         <v/>
       </c>
       <c r="K183" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L183" t="str">
         <v/>
@@ -15633,7 +15633,7 @@
         <v/>
       </c>
       <c r="D184" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -15654,7 +15654,7 @@
         <v/>
       </c>
       <c r="K184" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L184" t="str">
         <v/>
@@ -15668,14 +15668,14 @@
       <c r="O184">
         <v>0</v>
       </c>
-      <c r="P184" t="str">
-        <v/>
-      </c>
-      <c r="Q184" t="str">
-        <v/>
+      <c r="P184" s="1" t="d">
+        <v>2027-01-31T23:59:08.000Z</v>
+      </c>
+      <c r="Q184" s="1" t="d">
+        <v>2027-02-13T23:59:08.000Z</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S184" t="str">
         <v/>
@@ -15716,7 +15716,7 @@
         <v/>
       </c>
       <c r="D185" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -15737,7 +15737,7 @@
         <v/>
       </c>
       <c r="K185" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L185" t="str">
         <v/>
@@ -15752,13 +15752,13 @@
         <v>0</v>
       </c>
       <c r="P185" s="1" t="d">
-        <v>2027-01-31T23:59:08.000Z</v>
+        <v>2027-02-14T23:59:08.000Z</v>
       </c>
       <c r="Q185" s="1" t="d">
-        <v>2027-02-13T23:59:08.000Z</v>
+        <v>2027-02-14T23:59:08.000Z</v>
       </c>
       <c r="R185">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S185" t="str">
         <v/>
@@ -15799,7 +15799,7 @@
         <v/>
       </c>
       <c r="D186" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -15820,7 +15820,7 @@
         <v/>
       </c>
       <c r="K186" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L186" t="str">
         <v/>
@@ -15835,13 +15835,13 @@
         <v>0</v>
       </c>
       <c r="P186" s="1" t="d">
-        <v>2027-02-14T23:59:08.000Z</v>
+        <v>2027-02-17T23:59:08.000Z</v>
       </c>
       <c r="Q186" s="1" t="d">
-        <v>2027-02-14T23:59:08.000Z</v>
+        <v>2027-02-21T23:59:08.000Z</v>
       </c>
       <c r="R186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S186" t="str">
         <v/>
@@ -15873,16 +15873,16 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v/>
+        <v>RPA-026</v>
       </c>
       <c r="B187" t="str">
-        <v/>
+        <v>LOW</v>
       </c>
       <c r="C187" t="str">
         <v/>
       </c>
       <c r="D187" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -15903,7 +15903,7 @@
         <v/>
       </c>
       <c r="K187" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L187" t="str">
         <v/>
@@ -15918,13 +15918,13 @@
         <v>0</v>
       </c>
       <c r="P187" s="1" t="d">
-        <v>2027-02-17T23:59:08.000Z</v>
+        <v>2027-01-27T23:59:08.000Z</v>
       </c>
       <c r="Q187" s="1" t="d">
-        <v>2027-02-17T23:59:08.000Z</v>
+        <v>2027-02-21T23:59:08.000Z</v>
       </c>
       <c r="R187">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S187" t="str">
         <v/>
@@ -15936,7 +15936,7 @@
         <v>0</v>
       </c>
       <c r="V187" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W187" t="str">
         <v>No</v>
@@ -15956,16 +15956,16 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>RPA-026</v>
+        <v/>
       </c>
       <c r="B188" t="str">
-        <v>LOW</v>
+        <v/>
       </c>
       <c r="C188" t="str">
         <v/>
       </c>
       <c r="D188" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -15986,7 +15986,7 @@
         <v/>
       </c>
       <c r="K188" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L188" t="str">
         <v/>
@@ -16004,10 +16004,10 @@
         <v>2027-01-27T23:59:08.000Z</v>
       </c>
       <c r="Q188" s="1" t="d">
-        <v>2027-02-17T23:59:08.000Z</v>
+        <v>2027-01-30T23:59:08.000Z</v>
       </c>
       <c r="R188">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S188" t="str">
         <v/>
@@ -16019,7 +16019,7 @@
         <v>0</v>
       </c>
       <c r="V188" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W188" t="str">
         <v>No</v>
@@ -16048,7 +16048,7 @@
         <v/>
       </c>
       <c r="D189" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -16083,14 +16083,14 @@
       <c r="O189">
         <v>0</v>
       </c>
-      <c r="P189" s="1" t="d">
-        <v>2027-01-27T23:59:08.000Z</v>
-      </c>
-      <c r="Q189" s="1" t="d">
-        <v>2027-01-30T23:59:08.000Z</v>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
       </c>
       <c r="R189">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S189" t="str">
         <v/>
@@ -16131,7 +16131,7 @@
         <v/>
       </c>
       <c r="D190" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -16152,7 +16152,7 @@
         <v/>
       </c>
       <c r="K190" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L190" t="str">
         <v/>
@@ -16214,7 +16214,7 @@
         <v/>
       </c>
       <c r="D191" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -16235,7 +16235,7 @@
         <v/>
       </c>
       <c r="K191" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L191" t="str">
         <v/>
@@ -16249,14 +16249,14 @@
       <c r="O191">
         <v>0</v>
       </c>
-      <c r="P191" t="str">
-        <v/>
-      </c>
-      <c r="Q191" t="str">
-        <v/>
+      <c r="P191" s="1" t="d">
+        <v>2027-01-31T23:59:08.000Z</v>
+      </c>
+      <c r="Q191" s="1" t="d">
+        <v>2027-02-13T23:59:08.000Z</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S191" t="str">
         <v/>
@@ -16297,7 +16297,7 @@
         <v/>
       </c>
       <c r="D192" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -16318,7 +16318,7 @@
         <v/>
       </c>
       <c r="K192" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L192" t="str">
         <v/>
@@ -16333,13 +16333,13 @@
         <v>0</v>
       </c>
       <c r="P192" s="1" t="d">
-        <v>2027-01-31T23:59:08.000Z</v>
+        <v>2027-02-14T23:59:08.000Z</v>
       </c>
       <c r="Q192" s="1" t="d">
-        <v>2027-02-13T23:59:08.000Z</v>
+        <v>2027-02-14T23:59:08.000Z</v>
       </c>
       <c r="R192">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S192" t="str">
         <v/>
@@ -16380,7 +16380,7 @@
         <v/>
       </c>
       <c r="D193" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -16401,7 +16401,7 @@
         <v/>
       </c>
       <c r="K193" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L193" t="str">
         <v/>
@@ -16416,13 +16416,13 @@
         <v>0</v>
       </c>
       <c r="P193" s="1" t="d">
-        <v>2027-02-14T23:59:08.000Z</v>
+        <v>2027-02-17T23:59:08.000Z</v>
       </c>
       <c r="Q193" s="1" t="d">
-        <v>2027-02-14T23:59:08.000Z</v>
+        <v>2027-02-21T23:59:08.000Z</v>
       </c>
       <c r="R193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S193" t="str">
         <v/>
@@ -16454,16 +16454,16 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v/>
+        <v>RPA-027</v>
       </c>
       <c r="B194" t="str">
-        <v/>
+        <v>LOW</v>
       </c>
       <c r="C194" t="str">
         <v/>
       </c>
       <c r="D194" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -16484,7 +16484,7 @@
         <v/>
       </c>
       <c r="K194" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L194" t="str">
         <v/>
@@ -16499,13 +16499,13 @@
         <v>0</v>
       </c>
       <c r="P194" s="1" t="d">
-        <v>2027-02-17T23:59:08.000Z</v>
+        <v>2027-02-28T23:59:08.000Z</v>
       </c>
       <c r="Q194" s="1" t="d">
-        <v>2027-02-17T23:59:08.000Z</v>
+        <v>2027-03-23T23:59:08.000Z</v>
       </c>
       <c r="R194">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S194" t="str">
         <v/>
@@ -16517,7 +16517,7 @@
         <v>0</v>
       </c>
       <c r="V194" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W194" t="str">
         <v>No</v>
@@ -16537,16 +16537,16 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>RPA-027</v>
+        <v/>
       </c>
       <c r="B195" t="str">
-        <v>LOW</v>
+        <v/>
       </c>
       <c r="C195" t="str">
         <v/>
       </c>
       <c r="D195" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -16567,7 +16567,7 @@
         <v/>
       </c>
       <c r="K195" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L195" t="str">
         <v/>
@@ -16585,10 +16585,10 @@
         <v>2027-02-28T23:59:08.000Z</v>
       </c>
       <c r="Q195" s="1" t="d">
-        <v>2027-03-21T23:59:08.000Z</v>
+        <v>2027-03-01T23:59:08.000Z</v>
       </c>
       <c r="R195">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S195" t="str">
         <v/>
@@ -16600,7 +16600,7 @@
         <v>0</v>
       </c>
       <c r="V195" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W195" t="str">
         <v>No</v>
@@ -16629,7 +16629,7 @@
         <v/>
       </c>
       <c r="D196" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -16664,14 +16664,14 @@
       <c r="O196">
         <v>0</v>
       </c>
-      <c r="P196" s="1" t="d">
-        <v>2027-02-28T23:59:08.000Z</v>
-      </c>
-      <c r="Q196" s="1" t="d">
-        <v>2027-03-01T23:59:08.000Z</v>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
       </c>
       <c r="R196">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S196" t="str">
         <v/>
@@ -16712,7 +16712,7 @@
         <v/>
       </c>
       <c r="D197" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -16733,7 +16733,7 @@
         <v/>
       </c>
       <c r="K197" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L197" t="str">
         <v/>
@@ -16795,7 +16795,7 @@
         <v/>
       </c>
       <c r="D198" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -16816,7 +16816,7 @@
         <v/>
       </c>
       <c r="K198" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L198" t="str">
         <v/>
@@ -16830,14 +16830,14 @@
       <c r="O198">
         <v>0</v>
       </c>
-      <c r="P198" t="str">
-        <v/>
-      </c>
-      <c r="Q198" t="str">
-        <v/>
+      <c r="P198" s="1" t="d">
+        <v>2027-03-02T23:59:08.000Z</v>
+      </c>
+      <c r="Q198" s="1" t="d">
+        <v>2027-03-15T23:59:08.000Z</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S198" t="str">
         <v/>
@@ -16878,7 +16878,7 @@
         <v/>
       </c>
       <c r="D199" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -16899,7 +16899,7 @@
         <v/>
       </c>
       <c r="K199" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L199" t="str">
         <v/>
@@ -16914,13 +16914,13 @@
         <v>0</v>
       </c>
       <c r="P199" s="1" t="d">
-        <v>2027-03-02T23:59:08.000Z</v>
+        <v>2027-03-16T23:59:08.000Z</v>
       </c>
       <c r="Q199" s="1" t="d">
-        <v>2027-03-15T23:59:08.000Z</v>
+        <v>2027-03-16T23:59:08.000Z</v>
       </c>
       <c r="R199">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S199" t="str">
         <v/>
@@ -16961,7 +16961,7 @@
         <v/>
       </c>
       <c r="D200" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -16982,7 +16982,7 @@
         <v/>
       </c>
       <c r="K200" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L200" t="str">
         <v/>
@@ -16997,13 +16997,13 @@
         <v>0</v>
       </c>
       <c r="P200" s="1" t="d">
-        <v>2027-03-16T23:59:08.000Z</v>
+        <v>2027-03-21T23:59:08.000Z</v>
       </c>
       <c r="Q200" s="1" t="d">
-        <v>2027-03-16T23:59:08.000Z</v>
+        <v>2027-03-23T23:59:08.000Z</v>
       </c>
       <c r="R200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S200" t="str">
         <v/>
@@ -17035,16 +17035,16 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v/>
+        <v>RPA-028</v>
       </c>
       <c r="B201" t="str">
-        <v/>
+        <v>LOW</v>
       </c>
       <c r="C201" t="str">
         <v/>
       </c>
       <c r="D201" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -17065,7 +17065,7 @@
         <v/>
       </c>
       <c r="K201" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L201" t="str">
         <v/>
@@ -17080,13 +17080,13 @@
         <v>0</v>
       </c>
       <c r="P201" s="1" t="d">
-        <v>2027-03-21T23:59:08.000Z</v>
+        <v>2027-02-28T23:59:08.000Z</v>
       </c>
       <c r="Q201" s="1" t="d">
-        <v>2027-03-21T23:59:08.000Z</v>
+        <v>2027-03-23T23:59:08.000Z</v>
       </c>
       <c r="R201">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S201" t="str">
         <v/>
@@ -17098,7 +17098,7 @@
         <v>0</v>
       </c>
       <c r="V201" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W201" t="str">
         <v>No</v>
@@ -17118,16 +17118,16 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>RPA-028</v>
+        <v/>
       </c>
       <c r="B202" t="str">
-        <v>LOW</v>
+        <v/>
       </c>
       <c r="C202" t="str">
         <v/>
       </c>
       <c r="D202" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -17148,7 +17148,7 @@
         <v/>
       </c>
       <c r="K202" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L202" t="str">
         <v/>
@@ -17166,10 +17166,10 @@
         <v>2027-02-28T23:59:08.000Z</v>
       </c>
       <c r="Q202" s="1" t="d">
-        <v>2027-03-21T23:59:08.000Z</v>
+        <v>2027-03-01T23:59:08.000Z</v>
       </c>
       <c r="R202">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S202" t="str">
         <v/>
@@ -17181,7 +17181,7 @@
         <v>0</v>
       </c>
       <c r="V202" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W202" t="str">
         <v>No</v>
@@ -17210,7 +17210,7 @@
         <v/>
       </c>
       <c r="D203" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -17245,14 +17245,14 @@
       <c r="O203">
         <v>0</v>
       </c>
-      <c r="P203" s="1" t="d">
-        <v>2027-02-28T23:59:08.000Z</v>
-      </c>
-      <c r="Q203" s="1" t="d">
-        <v>2027-03-01T23:59:08.000Z</v>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" t="str">
+        <v/>
       </c>
       <c r="R203">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S203" t="str">
         <v/>
@@ -17293,7 +17293,7 @@
         <v/>
       </c>
       <c r="D204" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -17314,7 +17314,7 @@
         <v/>
       </c>
       <c r="K204" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L204" t="str">
         <v/>
@@ -17376,7 +17376,7 @@
         <v/>
       </c>
       <c r="D205" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -17397,7 +17397,7 @@
         <v/>
       </c>
       <c r="K205" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L205" t="str">
         <v/>
@@ -17411,14 +17411,14 @@
       <c r="O205">
         <v>0</v>
       </c>
-      <c r="P205" t="str">
-        <v/>
-      </c>
-      <c r="Q205" t="str">
-        <v/>
+      <c r="P205" s="1" t="d">
+        <v>2027-03-02T23:59:08.000Z</v>
+      </c>
+      <c r="Q205" s="1" t="d">
+        <v>2027-03-15T23:59:08.000Z</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S205" t="str">
         <v/>
@@ -17459,7 +17459,7 @@
         <v/>
       </c>
       <c r="D206" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -17480,7 +17480,7 @@
         <v/>
       </c>
       <c r="K206" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L206" t="str">
         <v/>
@@ -17495,13 +17495,13 @@
         <v>0</v>
       </c>
       <c r="P206" s="1" t="d">
-        <v>2027-03-02T23:59:08.000Z</v>
+        <v>2027-03-16T23:59:08.000Z</v>
       </c>
       <c r="Q206" s="1" t="d">
-        <v>2027-03-15T23:59:08.000Z</v>
+        <v>2027-03-16T23:59:08.000Z</v>
       </c>
       <c r="R206">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S206" t="str">
         <v/>
@@ -17542,7 +17542,7 @@
         <v/>
       </c>
       <c r="D207" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E207" t="str">
         <v/>
@@ -17563,7 +17563,7 @@
         <v/>
       </c>
       <c r="K207" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L207" t="str">
         <v/>
@@ -17578,13 +17578,13 @@
         <v>0</v>
       </c>
       <c r="P207" s="1" t="d">
-        <v>2027-03-16T23:59:08.000Z</v>
+        <v>2027-03-21T23:59:08.000Z</v>
       </c>
       <c r="Q207" s="1" t="d">
-        <v>2027-03-16T23:59:08.000Z</v>
+        <v>2027-03-23T23:59:08.000Z</v>
       </c>
       <c r="R207">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S207" t="str">
         <v/>
@@ -17616,16 +17616,16 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v/>
+        <v>RPA-029</v>
       </c>
       <c r="B208" t="str">
-        <v/>
+        <v>LOW</v>
       </c>
       <c r="C208" t="str">
         <v/>
       </c>
       <c r="D208" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E208" t="str">
         <v/>
@@ -17646,7 +17646,7 @@
         <v/>
       </c>
       <c r="K208" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L208" t="str">
         <v/>
@@ -17661,13 +17661,13 @@
         <v>0</v>
       </c>
       <c r="P208" s="1" t="d">
-        <v>2027-03-21T23:59:08.000Z</v>
+        <v>2027-03-30T23:59:08.000Z</v>
       </c>
       <c r="Q208" s="1" t="d">
-        <v>2027-03-21T23:59:08.000Z</v>
+        <v>2027-04-24T23:59:08.000Z</v>
       </c>
       <c r="R208">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S208" t="str">
         <v/>
@@ -17679,7 +17679,7 @@
         <v>0</v>
       </c>
       <c r="V208" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W208" t="str">
         <v>No</v>
@@ -17699,16 +17699,16 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>RPA-029</v>
+        <v/>
       </c>
       <c r="B209" t="str">
-        <v>LOW</v>
+        <v/>
       </c>
       <c r="C209" t="str">
         <v/>
       </c>
       <c r="D209" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E209" t="str">
         <v/>
@@ -17729,7 +17729,7 @@
         <v/>
       </c>
       <c r="K209" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L209" t="str">
         <v/>
@@ -17747,10 +17747,10 @@
         <v>2027-03-30T23:59:08.000Z</v>
       </c>
       <c r="Q209" s="1" t="d">
-        <v>2027-04-20T23:59:08.000Z</v>
+        <v>2027-03-31T23:59:08.000Z</v>
       </c>
       <c r="R209">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S209" t="str">
         <v/>
@@ -17762,7 +17762,7 @@
         <v>0</v>
       </c>
       <c r="V209" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W209" t="str">
         <v>No</v>
@@ -17791,7 +17791,7 @@
         <v/>
       </c>
       <c r="D210" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E210" t="str">
         <v/>
@@ -17826,14 +17826,14 @@
       <c r="O210">
         <v>0</v>
       </c>
-      <c r="P210" s="1" t="d">
-        <v>2027-03-30T23:59:08.000Z</v>
-      </c>
-      <c r="Q210" s="1" t="d">
-        <v>2027-03-31T23:59:08.000Z</v>
+      <c r="P210" t="str">
+        <v/>
+      </c>
+      <c r="Q210" t="str">
+        <v/>
       </c>
       <c r="R210">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S210" t="str">
         <v/>
@@ -17874,7 +17874,7 @@
         <v/>
       </c>
       <c r="D211" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E211" t="str">
         <v/>
@@ -17895,7 +17895,7 @@
         <v/>
       </c>
       <c r="K211" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L211" t="str">
         <v/>
@@ -17957,7 +17957,7 @@
         <v/>
       </c>
       <c r="D212" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E212" t="str">
         <v/>
@@ -17978,7 +17978,7 @@
         <v/>
       </c>
       <c r="K212" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L212" t="str">
         <v/>
@@ -17992,14 +17992,14 @@
       <c r="O212">
         <v>0</v>
       </c>
-      <c r="P212" t="str">
-        <v/>
-      </c>
-      <c r="Q212" t="str">
-        <v/>
+      <c r="P212" s="1" t="d">
+        <v>2027-04-03T23:59:08.000Z</v>
+      </c>
+      <c r="Q212" s="1" t="d">
+        <v>2027-04-14T23:59:08.000Z</v>
       </c>
       <c r="R212">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S212" t="str">
         <v/>
@@ -18040,7 +18040,7 @@
         <v/>
       </c>
       <c r="D213" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E213" t="str">
         <v/>
@@ -18061,7 +18061,7 @@
         <v/>
       </c>
       <c r="K213" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L213" t="str">
         <v/>
@@ -18076,13 +18076,13 @@
         <v>0</v>
       </c>
       <c r="P213" s="1" t="d">
-        <v>2027-04-03T23:59:08.000Z</v>
+        <v>2027-04-17T23:59:08.000Z</v>
       </c>
       <c r="Q213" s="1" t="d">
-        <v>2027-04-14T23:59:08.000Z</v>
+        <v>2027-04-17T23:59:08.000Z</v>
       </c>
       <c r="R213">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S213" t="str">
         <v/>
@@ -18123,7 +18123,7 @@
         <v/>
       </c>
       <c r="D214" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E214" t="str">
         <v/>
@@ -18144,7 +18144,7 @@
         <v/>
       </c>
       <c r="K214" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L214" t="str">
         <v/>
@@ -18159,13 +18159,13 @@
         <v>0</v>
       </c>
       <c r="P214" s="1" t="d">
-        <v>2027-04-17T23:59:08.000Z</v>
+        <v>2027-04-20T23:59:08.000Z</v>
       </c>
       <c r="Q214" s="1" t="d">
-        <v>2027-04-17T23:59:08.000Z</v>
+        <v>2027-04-24T23:59:08.000Z</v>
       </c>
       <c r="R214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S214" t="str">
         <v/>
@@ -18197,16 +18197,16 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v/>
+        <v>RPA-030</v>
       </c>
       <c r="B215" t="str">
-        <v/>
+        <v>LOW</v>
       </c>
       <c r="C215" t="str">
         <v/>
       </c>
       <c r="D215" t="str">
-        <v xml:space="preserve"> Go Live</v>
+        <v>Process Summary</v>
       </c>
       <c r="E215" t="str">
         <v/>
@@ -18227,7 +18227,7 @@
         <v/>
       </c>
       <c r="K215" t="str">
-        <v>Development Team – Proven</v>
+        <v/>
       </c>
       <c r="L215" t="str">
         <v/>
@@ -18242,13 +18242,13 @@
         <v>0</v>
       </c>
       <c r="P215" s="1" t="d">
-        <v>2027-04-20T23:59:08.000Z</v>
+        <v>2027-03-30T23:59:08.000Z</v>
       </c>
       <c r="Q215" s="1" t="d">
-        <v>2027-04-20T23:59:08.000Z</v>
+        <v>2027-04-24T23:59:08.000Z</v>
       </c>
       <c r="R215">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S215" t="str">
         <v/>
@@ -18260,7 +18260,7 @@
         <v>0</v>
       </c>
       <c r="V215" t="str">
-        <v>Red</v>
+        <v>Green</v>
       </c>
       <c r="W215" t="str">
         <v>No</v>
@@ -18280,16 +18280,16 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>RPA-030</v>
+        <v/>
       </c>
       <c r="B216" t="str">
-        <v>LOW</v>
+        <v/>
       </c>
       <c r="C216" t="str">
         <v/>
       </c>
       <c r="D216" t="str">
-        <v>Process Summary</v>
+        <v xml:space="preserve"> Assessment</v>
       </c>
       <c r="E216" t="str">
         <v/>
@@ -18310,7 +18310,7 @@
         <v/>
       </c>
       <c r="K216" t="str">
-        <v/>
+        <v>Business Analysis Team – Proven</v>
       </c>
       <c r="L216" t="str">
         <v/>
@@ -18328,10 +18328,10 @@
         <v>2027-03-30T23:59:08.000Z</v>
       </c>
       <c r="Q216" s="1" t="d">
-        <v>2027-04-20T23:59:08.000Z</v>
+        <v>2027-03-31T23:59:08.000Z</v>
       </c>
       <c r="R216">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S216" t="str">
         <v/>
@@ -18343,7 +18343,7 @@
         <v>0</v>
       </c>
       <c r="V216" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="W216" t="str">
         <v>No</v>
@@ -18372,7 +18372,7 @@
         <v/>
       </c>
       <c r="D217" t="str">
-        <v xml:space="preserve"> Assessment</v>
+        <v xml:space="preserve"> PDD Share</v>
       </c>
       <c r="E217" t="str">
         <v/>
@@ -18407,14 +18407,14 @@
       <c r="O217">
         <v>0</v>
       </c>
-      <c r="P217" s="1" t="d">
-        <v>2027-03-30T23:59:08.000Z</v>
-      </c>
-      <c r="Q217" s="1" t="d">
-        <v>2027-03-31T23:59:08.000Z</v>
+      <c r="P217" t="str">
+        <v/>
+      </c>
+      <c r="Q217" t="str">
+        <v/>
       </c>
       <c r="R217">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S217" t="str">
         <v/>
@@ -18455,7 +18455,7 @@
         <v/>
       </c>
       <c r="D218" t="str">
-        <v xml:space="preserve"> PDD Share</v>
+        <v xml:space="preserve"> PDD Approve</v>
       </c>
       <c r="E218" t="str">
         <v/>
@@ -18476,7 +18476,7 @@
         <v/>
       </c>
       <c r="K218" t="str">
-        <v>Business Analysis Team – Proven</v>
+        <v>Process Owner – RAC</v>
       </c>
       <c r="L218" t="str">
         <v/>
@@ -18538,7 +18538,7 @@
         <v/>
       </c>
       <c r="D219" t="str">
-        <v xml:space="preserve"> PDD Approve</v>
+        <v xml:space="preserve"> Development</v>
       </c>
       <c r="E219" t="str">
         <v/>
@@ -18559,7 +18559,7 @@
         <v/>
       </c>
       <c r="K219" t="str">
-        <v>Process Owner – RAC</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L219" t="str">
         <v/>
@@ -18573,14 +18573,14 @@
       <c r="O219">
         <v>0</v>
       </c>
-      <c r="P219" t="str">
-        <v/>
-      </c>
-      <c r="Q219" t="str">
-        <v/>
+      <c r="P219" s="1" t="d">
+        <v>2027-04-03T23:59:08.000Z</v>
+      </c>
+      <c r="Q219" s="1" t="d">
+        <v>2027-04-14T23:59:08.000Z</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S219" t="str">
         <v/>
@@ -18621,7 +18621,7 @@
         <v/>
       </c>
       <c r="D220" t="str">
-        <v xml:space="preserve"> Development</v>
+        <v xml:space="preserve"> UAT</v>
       </c>
       <c r="E220" t="str">
         <v/>
@@ -18642,7 +18642,7 @@
         <v/>
       </c>
       <c r="K220" t="str">
-        <v>Development Team – Proven</v>
+        <v>Proven Development Team / RAC SME</v>
       </c>
       <c r="L220" t="str">
         <v/>
@@ -18657,13 +18657,13 @@
         <v>0</v>
       </c>
       <c r="P220" s="1" t="d">
-        <v>2027-04-03T23:59:08.000Z</v>
+        <v>2027-04-17T23:59:08.000Z</v>
       </c>
       <c r="Q220" s="1" t="d">
-        <v>2027-04-14T23:59:08.000Z</v>
+        <v>2027-04-17T23:59:08.000Z</v>
       </c>
       <c r="R220">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S220" t="str">
         <v/>
@@ -18704,7 +18704,7 @@
         <v/>
       </c>
       <c r="D221" t="str">
-        <v xml:space="preserve"> UAT</v>
+        <v xml:space="preserve"> Go Live</v>
       </c>
       <c r="E221" t="str">
         <v/>
@@ -18725,7 +18725,7 @@
         <v/>
       </c>
       <c r="K221" t="str">
-        <v>Proven Development Team / RAC SME</v>
+        <v>Development Team – Proven</v>
       </c>
       <c r="L221" t="str">
         <v/>
@@ -18740,13 +18740,13 @@
         <v>0</v>
       </c>
       <c r="P221" s="1" t="d">
-        <v>2027-04-17T23:59:08.000Z</v>
+        <v>2027-04-20T23:59:08.000Z</v>
       </c>
       <c r="Q221" s="1" t="d">
-        <v>2027-04-17T23:59:08.000Z</v>
+        <v>2027-04-24T23:59:08.000Z</v>
       </c>
       <c r="R221">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S221" t="str">
         <v/>
@@ -18776,92 +18776,9 @@
         <v/>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v/>
-      </c>
-      <c r="B222" t="str">
-        <v/>
-      </c>
-      <c r="C222" t="str">
-        <v/>
-      </c>
-      <c r="D222" t="str">
-        <v xml:space="preserve"> Go Live</v>
-      </c>
-      <c r="E222" t="str">
-        <v/>
-      </c>
-      <c r="F222" t="str">
-        <v/>
-      </c>
-      <c r="G222" t="str">
-        <v/>
-      </c>
-      <c r="H222" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="I222" t="str">
-        <v/>
-      </c>
-      <c r="J222" t="str">
-        <v/>
-      </c>
-      <c r="K222" t="str">
-        <v>Development Team – Proven</v>
-      </c>
-      <c r="L222" t="str">
-        <v/>
-      </c>
-      <c r="M222" t="str">
-        <v/>
-      </c>
-      <c r="N222" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="O222">
-        <v>0</v>
-      </c>
-      <c r="P222" s="1" t="d">
-        <v>2027-04-20T23:59:08.000Z</v>
-      </c>
-      <c r="Q222" s="1" t="d">
-        <v>2027-04-20T23:59:08.000Z</v>
-      </c>
-      <c r="R222">
-        <v>1</v>
-      </c>
-      <c r="S222" t="str">
-        <v/>
-      </c>
-      <c r="T222" t="str">
-        <v/>
-      </c>
-      <c r="U222">
-        <v>0</v>
-      </c>
-      <c r="V222" t="str">
-        <v>Red</v>
-      </c>
-      <c r="W222" t="str">
-        <v>No</v>
-      </c>
-      <c r="X222" t="str">
-        <v/>
-      </c>
-      <c r="Y222" t="str">
-        <v/>
-      </c>
-      <c r="Z222" t="str">
-        <v/>
-      </c>
-      <c r="AA222" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA222"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA221"/>
   </ignoredErrors>
 </worksheet>
 </file>